--- a/results_for_analysis/plasmidfinder/plasmidfinder_summary_our_data.xlsx
+++ b/results_for_analysis/plasmidfinder/plasmidfinder_summary_our_data.xlsx
@@ -55,14 +55,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00BEDCBE"/>
-        <bgColor rgb="00BEDCBE"/>
+        <fgColor rgb="00BF2026"/>
+        <bgColor rgb="00BF2026"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00BF2026"/>
-        <bgColor rgb="00BF2026"/>
+        <fgColor rgb="00BEDCBE"/>
+        <bgColor rgb="00BEDCBE"/>
       </patternFill>
     </fill>
     <fill>
@@ -480,12 +480,12 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>rep13</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>rep21</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>rep13</t>
         </is>
       </c>
     </row>
@@ -497,12 +497,12 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
           <t>NODE_25_length_2765_cov_28.341547:1749..2465:rep21_20_p020(pLGA251)_FR821780:94.560669</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
     </row>
@@ -512,14 +512,14 @@
           <t>Q0003_MC00216</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>NODE_14_length_3640_cov_4152.396527:1..641:rep21_27_rep(pLNU4)_AM184102:57.512438</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
     </row>
@@ -531,12 +531,12 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
           <t>NODE_25_length_2765_cov_19.543973:301..1017:rep21_20_p020(pLGA251)_FR821780:94.560669</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
     </row>
@@ -546,14 +546,14 @@
           <t>Q0003_MC00201</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>NODE_23_length_3384_cov_162.948726:1800..2612:rep13_2_CDS39(pSSP1)_AP008935:97.833935</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>NODE_22_length_3640_cov_195.189866:1737..2724:rep21_27_rep(pLNU4)_AM184102:88.855721</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>NODE_23_length_3384_cov_162.948726:1800..2612:rep13_2_CDS39(pSSP1)_AP008935:97.833935</t>
         </is>
       </c>
     </row>
@@ -563,14 +563,14 @@
           <t>Q0003_MC00205</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>NODE_22_length_3384_cov_13.637089:2570..3382:rep13_2_CDS39(pSSP1)_AP008935:97.833935</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>NODE_21_length_3640_cov_66.074011:1772..2759:rep21_27_rep(pLNU4)_AM184102:88.855721</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>NODE_22_length_3384_cov_13.637089:2570..3382:rep13_2_CDS39(pSSP1)_AP008935:97.833935</t>
         </is>
       </c>
     </row>
@@ -582,12 +582,12 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
           <t>NODE_35_length_2724_cov_5405.487486:794..1789:rep21_24_rep(CN1_plasmid2)_NC_022227:99.899598</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
     </row>
@@ -597,14 +597,14 @@
           <t>R0047_MH0081</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>NODE_66_length_2532_cov_263.245322:1..689:rep21_1_rep(pWBG754)_GQ900396:63.563564</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
     </row>
@@ -614,14 +614,14 @@
           <t>Q0003_BC00211</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>NODE_27_length_3640_cov_751.392827:1..769:rep21_27_rep(pLNU4)_AM184102:69.064418</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
     </row>
@@ -631,14 +631,14 @@
           <t>R0051_BH00403</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>NODE_25_length_3384_cov_554.857231:1672..2484:rep13_2_CDS39(pSSP1)_AP008935:97.833935</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>NODE_24_length_3640_cov_548.830914:1014..2001:rep21_27_rep(pLNU4)_AM184102:88.855721</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>NODE_25_length_3384_cov_554.857231:1672..2484:rep13_2_CDS39(pSSP1)_AP008935:97.833935</t>
         </is>
       </c>
     </row>
@@ -650,12 +650,12 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
           <t>NODE_101_length_1483_cov_0.842920:273..989:rep21_20_p020(pLGA251)_FR821780:92.468619</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
     </row>
@@ -667,12 +667,12 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
           <t>NODE_27_length_3051_cov_11.101231:1749..2465:rep21_20_p020(pLGA251)_FR821780:94.560669</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
     </row>
@@ -682,14 +682,14 @@
           <t>Q0003_BC00410-2</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>NODE_12_length_2725_cov_2093.025019:616..1461:rep13_4_rep(pKH13)_EU170347:97.399527</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>NODE_9_length_35814_cov_51.069353:28235..29186:rep21_24_rep(CN1_plasmid2)_NC_022227:94.176707</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>NODE_12_length_2725_cov_2093.025019:616..1461:rep13_4_rep(pKH13)_EU170347:97.399527</t>
         </is>
       </c>
     </row>
@@ -699,14 +699,14 @@
           <t>Q0003_MC0026</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>NODE_29_length_3384_cov_193.679153:1852..2664:rep13_2_CDS39(pSSP1)_AP008935:97.833935</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>NODE_28_length_3640_cov_202.057785:882..1869:rep21_27_rep(pLNU4)_AM184102:88.855721</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>NODE_29_length_3384_cov_193.679153:1852..2664:rep13_2_CDS39(pSSP1)_AP008935:97.833935</t>
         </is>
       </c>
     </row>
@@ -718,12 +718,12 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
           <t>NODE_28_length_3640_cov_1107.717051:1710..2705:rep21_24_rep(CN1_plasmid2)_NC_022227:99.899598</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
     </row>
@@ -733,14 +733,14 @@
           <t>R0051_TC00505</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>NODE_24_length_3640_cov_4633.460575:794..1781:rep21_27_rep(pLNU4)_AM184102:88.855721, NODE_25_length_2576_cov_20.299714:1520..2236:rep21_20_p020(pLGA251)_FR821780:94.839609</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
     </row>
@@ -752,12 +752,12 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
           <t>NODE_22_length_9138_cov_1352.811897:6433..7428:rep21_24_rep(CN1_plasmid2)_NC_022227:99.899598</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
     </row>
@@ -767,14 +767,14 @@
           <t>Q0003_MC00211</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>NODE_17_length_3640_cov_3684.020780:3027..3631:rep21_27_rep(pLNU4)_AM184102:54.228856</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
     </row>
@@ -784,14 +784,14 @@
           <t>Q0003_BC00416</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>NODE_19_length_6648_cov_205.926085:1675..2457:rep21_19_rep(pLNU7)_AM399081:72.537313, NODE_19_length_6648_cov_205.926085:5506..6222:rep21_20_p020(pLGA251)_FR821780:96.513250</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
     </row>
@@ -803,12 +803,12 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
           <t>NODE_22_length_2765_cov_11.448825:1749..2465:rep21_20_p020(pLGA251)_FR821780:94.560669</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
     </row>
@@ -820,12 +820,12 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
           <t>NODE_25_length_2765_cov_14.235027:301..1017:rep21_20_p020(pLGA251)_FR821780:94.560669</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
     </row>
@@ -835,14 +835,14 @@
           <t>R0051_HK2002</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>NODE_85_length_2087_cov_1067.393878:1..921:rep21_22_CDS1(pUSA01)_NC007790:92.469880</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
     </row>
@@ -852,14 +852,14 @@
           <t>Q0003_BC00304</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>NODE_15_length_3640_cov_2230.854256:1103..2090:rep21_27_rep(pLNU4)_AM184102:88.855721</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
     </row>
@@ -869,14 +869,14 @@
           <t>Q0003_BC00406</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>NODE_33_length_5960_cov_8142.030002:27..917:rep21_4_repRC(pSK41)_AF051917:87.473684, NODE_33_length_5960_cov_8142.030002:27..917:rep21_5_repRC(pGO1)_FM207042:89.644013, NODE_33_length_5960_cov_8142.030002:2129..3124:rep21_24_rep(CN1_plasmid2)_NC_022227:97.690763</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
     </row>
@@ -888,12 +888,12 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
           <t>NODE_18_length_2423_cov_14.526568:1364..2080:rep21_20_p020(pLGA251)_FR821780:94.700139</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
     </row>
@@ -905,12 +905,12 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
           <t>NODE_19_length_19911_cov_17.969774:1749..2465:rep21_20_p020(pLGA251)_FR821780:94.560669, NODE_21_length_6682_cov_10.520519:2778..3773:rep21_24_rep(CN1_plasmid2)_NC_022227:99.899598</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
     </row>
@@ -922,12 +922,12 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
           <t>NODE_37_length_4617_cov_2.071269:2543..3259:rep21_20_p020(pLGA251)_FR821780:94.700139</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
     </row>
@@ -937,14 +937,14 @@
           <t>Q0003_MC00111</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>NODE_19_length_2420_cov_20.420410:1364..2080:rep21_20_p020(pLGA251)_FR821780:94.700139, NODE_26_length_962_cov_1.135329:1..960:rep21_27_rep(pLNU4)_AM184102:86.268657</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
     </row>
@@ -954,14 +954,14 @@
           <t>R0051_BC00306</t>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>NODE_63_length_3377_cov_5.877231:1772..2584:rep13_2_CDS39(pSSP1)_AP008935:97.833935</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>NODE_62_length_3640_cov_10.337319:1..653:rep21_27_rep(pLNU4)_AM184102:58.507463</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>NODE_63_length_3377_cov_5.877231:1772..2584:rep13_2_CDS39(pSSP1)_AP008935:97.833935</t>
         </is>
       </c>
     </row>
@@ -973,12 +973,12 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
           <t>NODE_28_length_2765_cov_10.953753:1749..2465:rep21_20_p020(pLGA251)_FR821780:94.560669</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
     </row>
@@ -988,14 +988,14 @@
           <t>Q0003_MC00214</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>NODE_26_length_3384_cov_104.065091:1672..2484:rep13_2_CDS39(pSSP1)_AP008935:97.833935</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>NODE_25_length_3640_cov_147.247652:1079..2066:rep21_27_rep(pLNU4)_AM184102:88.855721</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>NODE_26_length_3384_cov_104.065091:1672..2484:rep13_2_CDS39(pSSP1)_AP008935:97.833935</t>
         </is>
       </c>
     </row>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
           <t>NODE_68_length_2635_cov_3.496379:298..1014:rep21_20_p020(pLGA251)_FR821780:94.281729</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
     </row>
@@ -1022,14 +1022,14 @@
           <t>Q0003_MC00215</t>
         </is>
       </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>NODE_22_length_3384_cov_63.272029:2111..2923:rep13_2_CDS39(pSSP1)_AP008935:97.833935</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>NODE_21_length_3640_cov_7071.160262:2983..3640:rep21_27_rep(pLNU4)_AM184102:59.004975</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>NODE_22_length_3384_cov_63.272029:2111..2923:rep13_2_CDS39(pSSP1)_AP008935:97.833935</t>
         </is>
       </c>
     </row>
@@ -1058,12 +1058,12 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>rep7c</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>rep7a</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>rep7c</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>NODE_4_length_268507_cov_55.542663:135111..135930:rep7c_1_rep(MSSA476)_BX571857:98.418345</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>NODE_4_length_268507_cov_55.542663:135111..135930:rep7c_1_rep(MSSA476)_BX571857:98.418345</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1090,14 +1090,14 @@
           <t>Q0003_BC00105</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>NODE_24_length_4566_cov_448.628069:199..737:rep7a_10_ORF(pKH1)_SAU38656:94.561404</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
     </row>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>NODE_4_length_268507_cov_25.815232:135111..135930:rep7c_1_rep(MSSA476)_BX571857:98.418345</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>NODE_4_length_268507_cov_25.815232:135111..135930:rep7c_1_rep(MSSA476)_BX571857:98.418345</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1124,14 +1124,14 @@
           <t>Q0003_MC00201</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>NODE_20_length_4590_cov_65.132422:673..1422:rep7a_15_repC(pS0385p1)_AM990993:100.000000</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
     </row>
@@ -1141,14 +1141,14 @@
           <t>Q0003_BH404</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>NODE_43_length_767_cov_0.521875:99..767:rep7a_15_repC(pS0385p1)_AM990993:89.066667</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
     </row>
@@ -1160,12 +1160,12 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
           <t>NODE_19_length_4524_cov_85.657721:3293..4237:rep7a_17_CDS4(pS194)_NC005564:99.894180</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
     </row>
@@ -1175,14 +1175,14 @@
           <t>R0051_BC00101</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>NODE_29_length_3990_cov_3232.713694:482..1415:rep7a_5_repD(pTZ4)_NC010111:92.307692</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
     </row>
@@ -1192,14 +1192,14 @@
           <t>R0047_MH0081</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>NODE_47_length_11023_cov_6.337922:9115..9935:rep7c_1_rep(MSSA476)_BX571857:99.756395</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>NODE_57_length_4707_cov_6.418996:3806..4555:rep7a_15_repC(pS0385p1)_AM990993:98.933333</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>NODE_47_length_11023_cov_6.337922:9115..9935:rep7c_1_rep(MSSA476)_BX571857:99.756395</t>
         </is>
       </c>
     </row>
@@ -1211,12 +1211,12 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
           <t>NODE_23_length_4524_cov_1372.912895:1874..2818:rep7a_17_CDS4(pS194)_NC005564:99.894180</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
     </row>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
           <t>NODE_25_length_4524_cov_292.561747:1342..2286:rep7a_17_CDS4(pS194)_NC005564:99.894180</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
     </row>
@@ -1243,14 +1243,14 @@
           <t>R0051_BH00403</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>NODE_21_length_4590_cov_302.170513:672..1421:rep7a_15_repC(pS0385p1)_AM990993:100.000000</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
     </row>
@@ -1262,12 +1262,12 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>NODE_1_length_192950_cov_1.979702:132617..133436:rep7c_1_rep(MSSA476)_BX571857:98.418345</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>NODE_1_length_192950_cov_1.979702:132617..133436:rep7c_1_rep(MSSA476)_BX571857:98.418345</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1279,12 +1279,12 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>NODE_5_length_268507_cov_11.979052:135111..135930:rep7c_1_rep(MSSA476)_BX571857:98.418345</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>NODE_5_length_268507_cov_11.979052:135111..135930:rep7c_1_rep(MSSA476)_BX571857:98.418345</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1294,14 +1294,14 @@
           <t>Q0003_MC00105</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>NODE_33_length_4501_cov_77.803841:1634..2383:rep7a_15_repC(pS0385p1)_AM990993:100.000000</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
     </row>
@@ -1313,12 +1313,12 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>NODE_2_length_635514_cov_10.376311:366793..367613:rep7c_1_rep(MSSA476)_BX571857:99.634592</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>NODE_2_length_635514_cov_10.376311:366793..367613:rep7c_1_rep(MSSA476)_BX571857:99.634592</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1330,12 +1330,12 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
           <t>NODE_26_length_4524_cov_160.656811:588..1532:rep7a_17_CDS4(pS194)_NC005564:99.894180</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
     </row>
@@ -1345,14 +1345,14 @@
           <t>Q0003_BC00108</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>NODE_25_length_3920_cov_809.363828:412..1345:rep7a_5_repD(pTZ4)_NC010111:92.307692</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
     </row>
@@ -1362,14 +1362,14 @@
           <t>R0051_TC00505</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>NODE_4_length_277122_cov_30.730042:134259..135078:rep7c_1_rep(MSSA476)_BX571857:98.418345</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>NODE_21_length_4566_cov_5231.029286:126..664:rep7a_10_ORF(pKH1)_SAU38656:94.385965</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>NODE_4_length_277122_cov_30.730042:134259..135078:rep7c_1_rep(MSSA476)_BX571857:98.418345</t>
         </is>
       </c>
     </row>
@@ -1379,14 +1379,14 @@
           <t>Q0003_BC00110</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>NODE_27_length_3990_cov_1518.827595:2576..3509:rep7a_5_repD(pTZ4)_NC010111:92.307692</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
     </row>
@@ -1396,14 +1396,14 @@
           <t>R0047_TH0405</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>NODE_64_length_4566_cov_60.203875:2140..3084:rep7a_16_repC(Cassette)_AB037671:100.000000</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
     </row>
@@ -1413,14 +1413,14 @@
           <t>Q0003_BC00303</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>NODE_21_length_4501_cov_1227.056013:2522..3271:rep7a_15_repC(pS0385p1)_AM990993:100.000000</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
     </row>
@@ -1430,14 +1430,14 @@
           <t>Q0003_BC00416</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>NODE_22_length_4587_cov_114.164126:608..1357:rep7a_15_repC(pS0385p1)_AM990993:100.000000</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
     </row>
@@ -1447,14 +1447,14 @@
           <t>Q0003_BC00201</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>NODE_4_length_267825_cov_30.304111:132633..133452:rep7c_1_rep(MSSA476)_BX571857:98.418345</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>NODE_18_length_4902_cov_2227.063665:2912..3661:rep7a_15_repC(pS0385p1)_AM990993:100.000000, NODE_20_length_4524_cov_987.755288:1839..2783:rep7a_17_CDS4(pS194)_NC005564:100.000000</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>NODE_4_length_267825_cov_30.304111:132633..133452:rep7c_1_rep(MSSA476)_BX571857:98.418345</t>
         </is>
       </c>
     </row>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>NODE_4_length_268507_cov_27.116302:132578..133397:rep7c_1_rep(MSSA476)_BX571857:98.418345</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>NODE_4_length_268507_cov_27.116302:132578..133397:rep7c_1_rep(MSSA476)_BX571857:98.418345</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1483,12 +1483,12 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
           <t>NODE_14_length_4524_cov_684.118035:3079..4023:rep7a_17_CDS4(pS194)_NC005564:99.894180</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
     </row>
@@ -1498,14 +1498,14 @@
           <t>Q0003_BC00406</t>
         </is>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>NODE_35_length_4587_cov_2998.497534:3157..3906:rep7a_15_repC(pS0385p1)_AM990993:100.000000</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
     </row>
@@ -1515,14 +1515,14 @@
           <t>R0047_DABST013</t>
         </is>
       </c>
-      <c r="B28" s="4" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>NODE_60_length_1894_cov_1.265988:240..778:rep7a_10_ORF(pKH1)_SAU38656:94.561404</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
     </row>
@@ -1532,14 +1532,14 @@
           <t>Q0003_BC00118</t>
         </is>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
         <is>
           <t>NODE_42_length_4566_cov_377.889615:2727..3671:rep7a_16_repC(Cassette)_AB037671:100.000000</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
     </row>
@@ -1549,14 +1549,14 @@
           <t>R0051_TC00219</t>
         </is>
       </c>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>NODE_5_length_268541_cov_27.508025:135145..135964:rep7c_1_rep(MSSA476)_BX571857:98.418345</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
         <is>
           <t>NODE_22_length_4523_cov_608.903321:1..478:rep7a_18_rep(pS0385p2)_AM990994:62.963515</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>NODE_5_length_268541_cov_27.508025:135145..135964:rep7c_1_rep(MSSA476)_BX571857:98.418345</t>
         </is>
       </c>
     </row>
@@ -1566,14 +1566,14 @@
           <t>R0047_DADST035</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="inlineStr">
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>NODE_5_length_201040_cov_9.218921:49935..50755:rep7c_1_rep(MSSA476)_BX571857:100.000000</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1583,14 +1583,14 @@
           <t>Q0003_BC00117</t>
         </is>
       </c>
-      <c r="B32" s="5" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
         <is>
           <t>NODE_21_length_4566_cov_6749.945033:1221..2165:rep7a_16_repC(Cassette)_AB037671:100.000000</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
     </row>
@@ -1600,14 +1600,14 @@
           <t>R0051_BC00306</t>
         </is>
       </c>
-      <c r="B33" s="5" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>NODE_60_length_4501_cov_201.017375:139..888:rep7a_15_repC(pS0385p1)_AM990993:100.000000</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
     </row>
@@ -1619,12 +1619,12 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>NODE_4_length_268507_cov_25.484034:132578..133397:rep7c_1_rep(MSSA476)_BX571857:98.418345</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>NODE_4_length_268507_cov_25.484034:132578..133397:rep7c_1_rep(MSSA476)_BX571857:98.418345</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1636,12 +1636,12 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
           <t>NODE_23_length_4524_cov_31.321128:2278..3222:rep7a_17_CDS4(pS194)_NC005564:99.894180</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
     </row>
@@ -1651,14 +1651,14 @@
           <t>R0047_TC0201</t>
         </is>
       </c>
-      <c r="B36" s="5" t="inlineStr">
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>NODE_4_length_137025_cov_7.621923:127079..127898:rep7c_1_rep(MSSA476)_BX571857:98.418345</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
         <is>
           <t>NODE_59_length_4388_cov_133.696550:153..1097:rep7a_17_CDS4(pS194)_NC005564:100.000000</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>NODE_4_length_137025_cov_7.621923:127079..127898:rep7c_1_rep(MSSA476)_BX571857:98.418345</t>
         </is>
       </c>
     </row>
@@ -1670,12 +1670,12 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
           <t>NODE_19_length_4524_cov_2975.045486:2680..3624:rep7a_17_CDS4(pS194)_NC005564:99.894180</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
     </row>
@@ -1704,22 +1704,22 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>rep19</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>rep20</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>rep24b</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>rep15</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>rep20</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>rep19</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>rep24b</t>
         </is>
       </c>
     </row>
@@ -1729,7 +1729,7 @@
           <t>Q0003_BC00105</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -1739,12 +1739,12 @@
           <t>NODE_22_length_20530_cov_19.059060:16235..17224:rep20_3_rep(pTW20)_FN433597:100.000000</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -1756,22 +1756,22 @@
           <t>Q0003_BH404</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>NODE_28_length_26785_cov_14.218133:9177..10151:rep19_7_repA(SAP019A)_GQ900385:100.000000</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -1783,7 +1783,7 @@
           <t>R0051_DADST084</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -1793,12 +1793,12 @@
           <t>NODE_20_length_20530_cov_37.549331:1912..2901:rep20_3_rep(pTW20)_FN433597:100.000000</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -1810,24 +1810,24 @@
           <t>R0047_MH0081</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>NODE_30_length_27211_cov_18.172279:537..1520:rep19_13_rep(pBORa53)_AY917098:99.186992</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>NODE_76_length_1319_cov_5.442953:197..1133:rep15_1_repA(pLW043)_AE017171:95.265734</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>NODE_30_length_27211_cov_18.172279:537..1520:rep19_13_rep(pBORa53)_AY917098:99.186992</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
     </row>
@@ -1837,7 +1837,7 @@
           <t>R0051_DADST088</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -1847,12 +1847,12 @@
           <t>NODE_13_length_20530_cov_80.313434:12545..13534:rep20_3_rep(pTW20)_FN433597:100.000000</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -1864,24 +1864,24 @@
           <t>R0047_TH0405</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>NODE_27_length_35583_cov_14.364818:30208..31191:rep24b_1_rep(pWBG749)_GQ900391:99.898374</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>NODE_27_length_35583_cov_14.364818:30208..31191:rep24b_1_rep(pWBG749)_GQ900391:99.898374</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1891,7 +1891,7 @@
           <t>R0051_HK2002</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -1901,12 +1901,12 @@
           <t>NODE_63_length_7069_cov_93.045952:5079..6023:rep20_4_repA(SAP102A)_GQ900496:100.000000</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -1918,22 +1918,22 @@
           <t>R0051_TC00402</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>NODE_29_length_21479_cov_50.856220:1216..2114:rep20_10_repA(SAP057A)_NC013334:99.888765</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -1945,22 +1945,22 @@
           <t>R0047_DABST013</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>NODE_35_length_21480_cov_6.804852:1217..2115:rep20_10_repA(SAP057A)_NC013334:99.888765</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -1972,7 +1972,7 @@
           <t>Q0003_BC00118</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -1982,12 +1982,12 @@
           <t>NODE_32_length_20530_cov_13.891781:10827..11816:rep20_3_rep(pTW20)_FN433597:100.000000</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -1999,7 +1999,7 @@
           <t>Q0003_BC00117</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -2009,12 +2009,12 @@
           <t>NODE_19_length_20530_cov_119.409057:84..1073:rep20_3_rep(pTW20)_FN433597:100.000000</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -2060,12 +2060,12 @@
           <t>Q0003_BH404</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>NODE_28_length_26785_cov_14.218133:10577..11320:rep16_2_CDS6(pSJH101)_CP000737:99.731183, NODE_28_length_26785_cov_14.218133:10577..11320:rep16_5_SAP041A019(pWBG759)_GQ900401:99.731183</t>
         </is>
@@ -2077,7 +2077,7 @@
           <t>Q0003_TC00516</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -2094,12 +2094,12 @@
           <t>R0047_MH0081</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>NODE_30_length_27211_cov_18.172279:1946..2689:rep16_2_CDS6(pSJH101)_CP000737:98.790323, NODE_30_length_27211_cov_18.172279:1946..2689:rep16_5_SAP041A019(pWBG759)_GQ900401:98.790323</t>
         </is>
@@ -2111,7 +2111,7 @@
           <t>Q0003_MC00105</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -2128,12 +2128,12 @@
           <t>Q0003_BC00410-2</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>NODE_9_length_35814_cov_51.069353:1700..3274:repUS5_1_CDS20(pETB)_NC003265:99.301587</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -2145,7 +2145,7 @@
           <t>R0047_TH0405</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -2162,7 +2162,7 @@
           <t>Q0003_TC00523</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -2184,7 +2184,7 @@
           <t>NODE_29_length_21479_cov_50.856220:14530..16104:repUS5_1_CDS20(pETB)_NC003265:100.000000</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -2196,7 +2196,7 @@
           <t>Q0003_HB00604</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -2218,7 +2218,7 @@
           <t>NODE_35_length_21480_cov_6.804852:14531..16105:repUS5_1_CDS20(pETB)_NC003265:100.000000</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -2230,7 +2230,7 @@
           <t>Q0003_TC00522</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -2247,7 +2247,7 @@
           <t>R0051_BC00306</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -2283,17 +2283,17 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>rep18b</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>rep5c</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>rep18a</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>rep18b</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -2308,17 +2308,17 @@
           <t>Q0003_BH404</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -2335,17 +2335,17 @@
           <t>Q0003_TC00516</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -2362,22 +2362,22 @@
           <t>R0047_MH0081</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>NODE_30_length_27211_cov_18.172279:3977..4837:rep5a_1_repSAP001(pN315)_AP003139:99.535424</t>
         </is>
@@ -2389,17 +2389,17 @@
           <t>Q0003_MC00105</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -2416,17 +2416,17 @@
           <t>R0047_TH0405</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -2443,17 +2443,17 @@
           <t>Q0003_TC00523</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -2472,15 +2472,15 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
           <t>NODE_68_length_5302_cov_242.990338:437..1294:rep5c_1_rep(pRJ9)_AF447813:91.025641</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -2497,17 +2497,17 @@
           <t>Q0003_HB00604</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -2524,17 +2524,17 @@
           <t>Q0003_TC00522</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -2551,17 +2551,17 @@
           <t>R0051_BC00306</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -2578,22 +2578,22 @@
           <t>Q0003_BC00106</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>NODE_25_length_4170_cov_2.766394:2167..2693:rep18b_2_repA(pEF418)_AF408195:93.262411</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>NODE_24_length_4646_cov_1.198230:484..1414:rep18a_1_repA(p200B)_AB158402:96.784566</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>NODE_25_length_4170_cov_2.766394:2167..2693:rep18b_2_repA(pEF418)_AF408195:93.262411</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -2679,48 +2679,48 @@
           <t>Q0003_BC00102</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Rep1</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>rep21</t>
         </is>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" s="3" t="n">
         <v>94.56</v>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>717/717</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>NODE_25_length_2765_cov_28.341547</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>1749..2465</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>FR821780</t>
         </is>
       </c>
-      <c r="I2" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="I2" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>NODE_25_length_2765_cov_28.341547:1749..2465:rep21_20_p020(pLGA251)_FR821780:94.560669</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>1..717</t>
         </is>
@@ -2732,48 +2732,48 @@
           <t>Q0003_BC00102</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Rep_trans</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>rep7c</t>
         </is>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" s="3" t="n">
         <v>98.54000000000001</v>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>821/821</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>NODE_4_length_268507_cov_55.542663</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>135111..135930</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>BX571857</t>
         </is>
       </c>
-      <c r="I3" s="2" t="n">
+      <c r="I3" s="3" t="n">
         <v>99.88</v>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>NODE_4_length_268507_cov_55.542663:135111..135930:rep7c_1_rep(MSSA476)_BX571857:98.418345</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>1..821</t>
         </is>
@@ -2891,48 +2891,48 @@
           <t>Q0003_MC00216</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Rep1</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>rep21</t>
         </is>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="D6" s="2" t="n">
         <v>90.17</v>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>641/1005</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>NODE_14_length_3640_cov_4152.396527</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>1..641</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>AM184102</t>
         </is>
       </c>
-      <c r="I6" s="3" t="n">
+      <c r="I6" s="2" t="n">
         <v>63.78</v>
       </c>
-      <c r="J6" s="3" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>NODE_14_length_3640_cov_4152.396527:1..641:rep21_27_rep(pLNU4)_AM184102:57.512438</t>
         </is>
       </c>
-      <c r="K6" s="3" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>1..641</t>
         </is>
@@ -2944,48 +2944,48 @@
           <t>Q0003_TC00512</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Rep1</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>rep21</t>
         </is>
       </c>
-      <c r="D7" s="2" t="n">
+      <c r="D7" s="3" t="n">
         <v>94.56</v>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>717/717</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>NODE_25_length_2765_cov_19.543973</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>301..1017</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H7" s="3" t="inlineStr">
         <is>
           <t>FR821780</t>
         </is>
       </c>
-      <c r="I7" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="I7" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
         <is>
           <t>NODE_25_length_2765_cov_19.543973:301..1017:rep21_20_p020(pLGA251)_FR821780:94.560669</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="K7" s="3" t="inlineStr">
         <is>
           <t>1..717</t>
         </is>
@@ -2997,48 +2997,48 @@
           <t>Q0003_TC00512</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>Rep_trans</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>rep7c</t>
         </is>
       </c>
-      <c r="D8" s="2" t="n">
+      <c r="D8" s="3" t="n">
         <v>98.54000000000001</v>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>821/821</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>NODE_4_length_268507_cov_25.815232</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" s="3" t="inlineStr">
         <is>
           <t>135111..135930</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H8" s="3" t="inlineStr">
         <is>
           <t>BX571857</t>
         </is>
       </c>
-      <c r="I8" s="2" t="n">
+      <c r="I8" s="3" t="n">
         <v>99.88</v>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="J8" s="3" t="inlineStr">
         <is>
           <t>NODE_4_length_268507_cov_25.815232:135111..135930:rep7c_1_rep(MSSA476)_BX571857:98.418345</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="K8" s="3" t="inlineStr">
         <is>
           <t>1..821</t>
         </is>
@@ -3050,48 +3050,48 @@
           <t>Q0003_MC00201</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Rep1</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>rep21</t>
         </is>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="D9" s="2" t="n">
         <v>90.38</v>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>988/1005</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>NODE_22_length_3640_cov_195.189866</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>1737..2724</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>AM184102</t>
         </is>
       </c>
-      <c r="I9" s="3" t="n">
+      <c r="I9" s="2" t="n">
         <v>98.31</v>
       </c>
-      <c r="J9" s="3" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>NODE_22_length_3640_cov_195.189866:1737..2724:rep21_27_rep(pLNU4)_AM184102:88.855721</t>
         </is>
       </c>
-      <c r="K9" s="3" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>1..988</t>
         </is>
@@ -3209,48 +3209,48 @@
           <t>Q0003_BH404</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>Inc18</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>rep16</t>
         </is>
       </c>
-      <c r="D12" s="2" t="n">
+      <c r="D12" s="3" t="n">
         <v>99.73</v>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
         <is>
           <t>744/744</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>NODE_28_length_26785_cov_14.218133</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G12" s="3" t="inlineStr">
         <is>
           <t>10577..11320</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H12" s="3" t="inlineStr">
         <is>
           <t>CP000737</t>
         </is>
       </c>
-      <c r="I12" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="I12" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
         <is>
           <t>NODE_28_length_26785_cov_14.218133:10577..11320:rep16_2_CDS6(pSJH101)_CP000737:99.731183</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="K12" s="3" t="inlineStr">
         <is>
           <t>1..744</t>
         </is>
@@ -3262,48 +3262,48 @@
           <t>Q0003_BH404</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>Inc18</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>rep16</t>
         </is>
       </c>
-      <c r="D13" s="2" t="n">
+      <c r="D13" s="3" t="n">
         <v>99.73</v>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>744/744</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>NODE_28_length_26785_cov_14.218133</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>10577..11320</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H13" s="3" t="inlineStr">
         <is>
           <t>GQ900401</t>
         </is>
       </c>
-      <c r="I13" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="I13" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
         <is>
           <t>NODE_28_length_26785_cov_14.218133:10577..11320:rep16_5_SAP041A019(pWBG759)_GQ900401:99.731183</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="K13" s="3" t="inlineStr">
         <is>
           <t>1..744</t>
         </is>
@@ -3527,48 +3527,48 @@
           <t>Q0003_MC00205</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>Rep1</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>rep21</t>
         </is>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="D18" s="2" t="n">
         <v>90.38</v>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>988/1005</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>NODE_21_length_3640_cov_66.074011</t>
         </is>
       </c>
-      <c r="G18" s="3" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>1772..2759</t>
         </is>
       </c>
-      <c r="H18" s="3" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>AM184102</t>
         </is>
       </c>
-      <c r="I18" s="3" t="n">
+      <c r="I18" s="2" t="n">
         <v>98.31</v>
       </c>
-      <c r="J18" s="3" t="inlineStr">
+      <c r="J18" s="2" t="inlineStr">
         <is>
           <t>NODE_21_length_3640_cov_66.074011:1772..2759:rep21_27_rep(pLNU4)_AM184102:88.855721</t>
         </is>
       </c>
-      <c r="K18" s="3" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>1..988</t>
         </is>
@@ -3633,48 +3633,48 @@
           <t>Q0003_MC00205</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>Rep_trans</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>rep7a</t>
         </is>
       </c>
-      <c r="D20" s="2" t="n">
+      <c r="D20" s="3" t="n">
         <v>99.89</v>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t>945/945</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F20" s="3" t="inlineStr">
         <is>
           <t>NODE_19_length_4524_cov_85.657721</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G20" s="3" t="inlineStr">
         <is>
           <t>3293..4237</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="H20" s="3" t="inlineStr">
         <is>
           <t>NC005564</t>
         </is>
       </c>
-      <c r="I20" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="I20" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
         <is>
           <t>NODE_19_length_4524_cov_85.657721:3293..4237:rep7a_17_CDS4(pS194)_NC005564:99.894180</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="K20" s="3" t="inlineStr">
         <is>
           <t>1..945</t>
         </is>
@@ -3845,48 +3845,48 @@
           <t>R0051_BC00101</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>Rep1</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>rep21</t>
         </is>
       </c>
-      <c r="D24" s="2" t="n">
+      <c r="D24" s="3" t="n">
         <v>99.90000000000001</v>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E24" s="3" t="inlineStr">
         <is>
           <t>996/996</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F24" s="3" t="inlineStr">
         <is>
           <t>NODE_35_length_2724_cov_5405.487486</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G24" s="3" t="inlineStr">
         <is>
           <t>794..1789</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="H24" s="3" t="inlineStr">
         <is>
           <t>plasmid2)NC022227</t>
         </is>
       </c>
-      <c r="I24" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="I24" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
         <is>
           <t>NODE_35_length_2724_cov_5405.487486:794..1789:rep21_24_rep(CN1_plasmid2)_NC_022227:99.899598</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr">
+      <c r="K24" s="3" t="inlineStr">
         <is>
           <t>1..996</t>
         </is>
@@ -3898,48 +3898,48 @@
           <t>R0051_BC00101</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>Rep_trans</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>rep7a</t>
         </is>
       </c>
-      <c r="D25" s="3" t="n">
+      <c r="D25" s="2" t="n">
         <v>92.51000000000001</v>
       </c>
-      <c r="E25" s="3" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>934/936</t>
         </is>
       </c>
-      <c r="F25" s="3" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>NODE_29_length_3990_cov_3232.713694</t>
         </is>
       </c>
-      <c r="G25" s="3" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>482..1415</t>
         </is>
       </c>
-      <c r="H25" s="3" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>NC010111</t>
         </is>
       </c>
-      <c r="I25" s="3" t="n">
+      <c r="I25" s="2" t="n">
         <v>99.79000000000001</v>
       </c>
-      <c r="J25" s="3" t="inlineStr">
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>NODE_29_length_3990_cov_3232.713694:482..1415:rep7a_5_repD(pTZ4)_NC010111:92.307692</t>
         </is>
       </c>
-      <c r="K25" s="3" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>1..934</t>
         </is>
@@ -3951,48 +3951,48 @@
           <t>R0047_MH0081</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>Inc18</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>rep16</t>
         </is>
       </c>
-      <c r="D26" s="2" t="n">
+      <c r="D26" s="3" t="n">
         <v>98.79000000000001</v>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E26" s="3" t="inlineStr">
         <is>
           <t>744/744</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F26" s="3" t="inlineStr">
         <is>
           <t>NODE_30_length_27211_cov_18.172279</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G26" s="3" t="inlineStr">
         <is>
           <t>1946..2689</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="H26" s="3" t="inlineStr">
         <is>
           <t>CP000737</t>
         </is>
       </c>
-      <c r="I26" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
+      <c r="I26" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
         <is>
           <t>NODE_30_length_27211_cov_18.172279:1946..2689:rep16_2_CDS6(pSJH101)_CP000737:98.790323</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr">
+      <c r="K26" s="3" t="inlineStr">
         <is>
           <t>1..744</t>
         </is>
@@ -4004,48 +4004,48 @@
           <t>R0047_MH0081</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>Inc18</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>rep16</t>
         </is>
       </c>
-      <c r="D27" s="2" t="n">
+      <c r="D27" s="3" t="n">
         <v>98.79000000000001</v>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E27" s="3" t="inlineStr">
         <is>
           <t>744/744</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F27" s="3" t="inlineStr">
         <is>
           <t>NODE_30_length_27211_cov_18.172279</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="G27" s="3" t="inlineStr">
         <is>
           <t>1946..2689</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="H27" s="3" t="inlineStr">
         <is>
           <t>GQ900401</t>
         </is>
       </c>
-      <c r="I27" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
+      <c r="I27" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
         <is>
           <t>NODE_30_length_27211_cov_18.172279:1946..2689:rep16_5_SAP041A019(pWBG759)_GQ900401:98.790323</t>
         </is>
       </c>
-      <c r="K27" s="2" t="inlineStr">
+      <c r="K27" s="3" t="inlineStr">
         <is>
           <t>1..744</t>
         </is>
@@ -4057,48 +4057,48 @@
           <t>R0047_MH0081</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>Rep1</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>rep21</t>
         </is>
       </c>
-      <c r="D28" s="3" t="n">
+      <c r="D28" s="2" t="n">
         <v>92.16</v>
       </c>
-      <c r="E28" s="3" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>689/999</t>
         </is>
       </c>
-      <c r="F28" s="3" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>NODE_66_length_2532_cov_263.245322</t>
         </is>
       </c>
-      <c r="G28" s="3" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>1..689</t>
         </is>
       </c>
-      <c r="H28" s="3" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>GQ900396</t>
         </is>
       </c>
-      <c r="I28" s="3" t="n">
+      <c r="I28" s="2" t="n">
         <v>68.97</v>
       </c>
-      <c r="J28" s="3" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>NODE_66_length_2532_cov_263.245322:1..689:rep21_1_rep(pWBG754)_GQ900396:63.563564</t>
         </is>
       </c>
-      <c r="K28" s="3" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>1..689</t>
         </is>
@@ -4110,48 +4110,48 @@
           <t>R0047_MH0081</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>Rep3</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>rep5a</t>
         </is>
       </c>
-      <c r="D29" s="2" t="n">
+      <c r="D29" s="3" t="n">
         <v>99.54000000000001</v>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E29" s="3" t="inlineStr">
         <is>
           <t>861/861</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F29" s="3" t="inlineStr">
         <is>
           <t>NODE_30_length_27211_cov_18.172279</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="G29" s="3" t="inlineStr">
         <is>
           <t>3977..4837</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="H29" s="3" t="inlineStr">
         <is>
           <t>AP003139</t>
         </is>
       </c>
-      <c r="I29" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
+      <c r="I29" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
         <is>
           <t>NODE_30_length_27211_cov_18.172279:3977..4837:rep5a_1_repSAP001(pN315)_AP003139:99.535424</t>
         </is>
       </c>
-      <c r="K29" s="2" t="inlineStr">
+      <c r="K29" s="3" t="inlineStr">
         <is>
           <t>1..861</t>
         </is>
@@ -4163,48 +4163,48 @@
           <t>R0047_MH0081</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>RepA_N</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C30" s="3" t="inlineStr">
         <is>
           <t>rep19</t>
         </is>
       </c>
-      <c r="D30" s="2" t="n">
+      <c r="D30" s="3" t="n">
         <v>99.19</v>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E30" s="3" t="inlineStr">
         <is>
           <t>984/984</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F30" s="3" t="inlineStr">
         <is>
           <t>NODE_30_length_27211_cov_18.172279</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G30" s="3" t="inlineStr">
         <is>
           <t>537..1520</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="H30" s="3" t="inlineStr">
         <is>
           <t>AY917098</t>
         </is>
       </c>
-      <c r="I30" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
+      <c r="I30" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
         <is>
           <t>NODE_30_length_27211_cov_18.172279:537..1520:rep19_13_rep(pBORa53)_AY917098:99.186992</t>
         </is>
       </c>
-      <c r="K30" s="2" t="inlineStr">
+      <c r="K30" s="3" t="inlineStr">
         <is>
           <t>1..984</t>
         </is>
@@ -4216,48 +4216,48 @@
           <t>R0047_MH0081</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>RepA_N</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr">
         <is>
           <t>rep15</t>
         </is>
       </c>
-      <c r="D31" s="2" t="n">
+      <c r="D31" s="3" t="n">
         <v>97.59999999999999</v>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E31" s="3" t="inlineStr">
         <is>
           <t>960/960</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F31" s="3" t="inlineStr">
         <is>
           <t>NODE_76_length_1319_cov_5.442953</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="G31" s="3" t="inlineStr">
         <is>
           <t>197..1133</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="H31" s="3" t="inlineStr">
         <is>
           <t>AE017171</t>
         </is>
       </c>
-      <c r="I31" s="2" t="n">
+      <c r="I31" s="3" t="n">
         <v>97.59999999999999</v>
       </c>
-      <c r="J31" s="2" t="inlineStr">
+      <c r="J31" s="3" t="inlineStr">
         <is>
           <t>NODE_76_length_1319_cov_5.442953:197..1133:rep15_1_repA(pLW043)_AE017171:95.265734</t>
         </is>
       </c>
-      <c r="K31" s="2" t="inlineStr">
+      <c r="K31" s="3" t="inlineStr">
         <is>
           <t>1..960</t>
         </is>
@@ -4322,48 +4322,48 @@
           <t>R0047_MH0081</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>Rep_trans</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="C33" s="3" t="inlineStr">
         <is>
           <t>rep7c</t>
         </is>
       </c>
-      <c r="D33" s="2" t="n">
+      <c r="D33" s="3" t="n">
         <v>99.76000000000001</v>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E33" s="3" t="inlineStr">
         <is>
           <t>821/821</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F33" s="3" t="inlineStr">
         <is>
           <t>NODE_47_length_11023_cov_6.337922</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="G33" s="3" t="inlineStr">
         <is>
           <t>9115..9935</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="H33" s="3" t="inlineStr">
         <is>
           <t>BX571857</t>
         </is>
       </c>
-      <c r="I33" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
+      <c r="I33" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
         <is>
           <t>NODE_47_length_11023_cov_6.337922:9115..9935:rep7c_1_rep(MSSA476)_BX571857:99.756395</t>
         </is>
       </c>
-      <c r="K33" s="2" t="inlineStr">
+      <c r="K33" s="3" t="inlineStr">
         <is>
           <t>1..821</t>
         </is>
@@ -4375,48 +4375,48 @@
           <t>R0047_MH0081</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B34" s="3" t="inlineStr">
         <is>
           <t>Rep_trans</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="C34" s="3" t="inlineStr">
         <is>
           <t>rep7a</t>
         </is>
       </c>
-      <c r="D34" s="2" t="n">
+      <c r="D34" s="3" t="n">
         <v>98.93000000000001</v>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E34" s="3" t="inlineStr">
         <is>
           <t>750/750</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F34" s="3" t="inlineStr">
         <is>
           <t>NODE_57_length_4707_cov_6.418996</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G34" s="3" t="inlineStr">
         <is>
           <t>3806..4555</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="H34" s="3" t="inlineStr">
         <is>
           <t>AM990993</t>
         </is>
       </c>
-      <c r="I34" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
+      <c r="I34" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
         <is>
           <t>NODE_57_length_4707_cov_6.418996:3806..4555:rep7a_15_repC(pS0385p1)_AM990993:98.933333</t>
         </is>
       </c>
-      <c r="K34" s="2" t="inlineStr">
+      <c r="K34" s="3" t="inlineStr">
         <is>
           <t>1..750</t>
         </is>
@@ -4481,48 +4481,48 @@
           <t>Q0003_MC00210</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B36" s="3" t="inlineStr">
         <is>
           <t>Rep_trans</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="C36" s="3" t="inlineStr">
         <is>
           <t>rep7a</t>
         </is>
       </c>
-      <c r="D36" s="2" t="n">
+      <c r="D36" s="3" t="n">
         <v>99.89</v>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E36" s="3" t="inlineStr">
         <is>
           <t>945/945</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F36" s="3" t="inlineStr">
         <is>
           <t>NODE_23_length_4524_cov_1372.912895</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G36" s="3" t="inlineStr">
         <is>
           <t>1874..2818</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="H36" s="3" t="inlineStr">
         <is>
           <t>NC005564</t>
         </is>
       </c>
-      <c r="I36" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
+      <c r="I36" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
         <is>
           <t>NODE_23_length_4524_cov_1372.912895:1874..2818:rep7a_17_CDS4(pS194)_NC005564:99.894180</t>
         </is>
       </c>
-      <c r="K36" s="2" t="inlineStr">
+      <c r="K36" s="3" t="inlineStr">
         <is>
           <t>1..945</t>
         </is>
@@ -4534,48 +4534,48 @@
           <t>Q0003_BC00211</t>
         </is>
       </c>
-      <c r="B37" s="3" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>Rep1</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
         <is>
           <t>rep21</t>
         </is>
       </c>
-      <c r="D37" s="3" t="n">
+      <c r="D37" s="2" t="n">
         <v>90.26000000000001</v>
       </c>
-      <c r="E37" s="3" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>770/1005</t>
         </is>
       </c>
-      <c r="F37" s="3" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>NODE_27_length_3640_cov_751.392827</t>
         </is>
       </c>
-      <c r="G37" s="3" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr">
         <is>
           <t>1..769</t>
         </is>
       </c>
-      <c r="H37" s="3" t="inlineStr">
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>AM184102</t>
         </is>
       </c>
-      <c r="I37" s="3" t="n">
+      <c r="I37" s="2" t="n">
         <v>76.52</v>
       </c>
-      <c r="J37" s="3" t="inlineStr">
+      <c r="J37" s="2" t="inlineStr">
         <is>
           <t>NODE_27_length_3640_cov_751.392827:1..769:rep21_27_rep(pLNU4)_AM184102:69.064418</t>
         </is>
       </c>
-      <c r="K37" s="3" t="inlineStr">
+      <c r="K37" s="2" t="inlineStr">
         <is>
           <t>1..770</t>
         </is>
@@ -4587,48 +4587,48 @@
           <t>Q0003_BC00211</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B38" s="3" t="inlineStr">
         <is>
           <t>Rep_trans</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="C38" s="3" t="inlineStr">
         <is>
           <t>rep7a</t>
         </is>
       </c>
-      <c r="D38" s="2" t="n">
+      <c r="D38" s="3" t="n">
         <v>99.89</v>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E38" s="3" t="inlineStr">
         <is>
           <t>945/945</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F38" s="3" t="inlineStr">
         <is>
           <t>NODE_25_length_4524_cov_292.561747</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G38" s="3" t="inlineStr">
         <is>
           <t>1342..2286</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="H38" s="3" t="inlineStr">
         <is>
           <t>NC005564</t>
         </is>
       </c>
-      <c r="I38" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
+      <c r="I38" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
         <is>
           <t>NODE_25_length_4524_cov_292.561747:1342..2286:rep7a_17_CDS4(pS194)_NC005564:99.894180</t>
         </is>
       </c>
-      <c r="K38" s="2" t="inlineStr">
+      <c r="K38" s="3" t="inlineStr">
         <is>
           <t>1..945</t>
         </is>
@@ -4640,48 +4640,48 @@
           <t>R0051_BH00403</t>
         </is>
       </c>
-      <c r="B39" s="3" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>Rep1</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
         <is>
           <t>rep21</t>
         </is>
       </c>
-      <c r="D39" s="3" t="n">
+      <c r="D39" s="2" t="n">
         <v>90.38</v>
       </c>
-      <c r="E39" s="3" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>988/1005</t>
         </is>
       </c>
-      <c r="F39" s="3" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>NODE_24_length_3640_cov_548.830914</t>
         </is>
       </c>
-      <c r="G39" s="3" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr">
         <is>
           <t>1014..2001</t>
         </is>
       </c>
-      <c r="H39" s="3" t="inlineStr">
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>AM184102</t>
         </is>
       </c>
-      <c r="I39" s="3" t="n">
+      <c r="I39" s="2" t="n">
         <v>98.31</v>
       </c>
-      <c r="J39" s="3" t="inlineStr">
+      <c r="J39" s="2" t="inlineStr">
         <is>
           <t>NODE_24_length_3640_cov_548.830914:1014..2001:rep21_27_rep(pLNU4)_AM184102:88.855721</t>
         </is>
       </c>
-      <c r="K39" s="3" t="inlineStr">
+      <c r="K39" s="2" t="inlineStr">
         <is>
           <t>1..988</t>
         </is>
@@ -4799,48 +4799,48 @@
           <t>Q0003_BC00310</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B42" s="3" t="inlineStr">
         <is>
           <t>Rep1</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
+      <c r="C42" s="3" t="inlineStr">
         <is>
           <t>rep21</t>
         </is>
       </c>
-      <c r="D42" s="2" t="n">
+      <c r="D42" s="3" t="n">
         <v>92.47</v>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E42" s="3" t="inlineStr">
         <is>
           <t>717/717</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F42" s="3" t="inlineStr">
         <is>
           <t>NODE_101_length_1483_cov_0.842920</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="G42" s="3" t="inlineStr">
         <is>
           <t>273..989</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="H42" s="3" t="inlineStr">
         <is>
           <t>FR821780</t>
         </is>
       </c>
-      <c r="I42" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
+      <c r="I42" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
         <is>
           <t>NODE_101_length_1483_cov_0.842920:273..989:rep21_20_p020(pLGA251)_FR821780:92.468619</t>
         </is>
       </c>
-      <c r="K42" s="2" t="inlineStr">
+      <c r="K42" s="3" t="inlineStr">
         <is>
           <t>1..717</t>
         </is>
@@ -4852,48 +4852,48 @@
           <t>Q0003_BC00310</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B43" s="3" t="inlineStr">
         <is>
           <t>Rep_trans</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
+      <c r="C43" s="3" t="inlineStr">
         <is>
           <t>rep7c</t>
         </is>
       </c>
-      <c r="D43" s="2" t="n">
+      <c r="D43" s="3" t="n">
         <v>98.54000000000001</v>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E43" s="3" t="inlineStr">
         <is>
           <t>821/821</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F43" s="3" t="inlineStr">
         <is>
           <t>NODE_1_length_192950_cov_1.979702</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr">
+      <c r="G43" s="3" t="inlineStr">
         <is>
           <t>132617..133436</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="H43" s="3" t="inlineStr">
         <is>
           <t>BX571857</t>
         </is>
       </c>
-      <c r="I43" s="2" t="n">
+      <c r="I43" s="3" t="n">
         <v>99.88</v>
       </c>
-      <c r="J43" s="2" t="inlineStr">
+      <c r="J43" s="3" t="inlineStr">
         <is>
           <t>NODE_1_length_192950_cov_1.979702:132617..133436:rep7c_1_rep(MSSA476)_BX571857:98.418345</t>
         </is>
       </c>
-      <c r="K43" s="2" t="inlineStr">
+      <c r="K43" s="3" t="inlineStr">
         <is>
           <t>1..821</t>
         </is>
@@ -4905,48 +4905,48 @@
           <t>Q0003_BC00104</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B44" s="3" t="inlineStr">
         <is>
           <t>Rep1</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
+      <c r="C44" s="3" t="inlineStr">
         <is>
           <t>rep21</t>
         </is>
       </c>
-      <c r="D44" s="2" t="n">
+      <c r="D44" s="3" t="n">
         <v>94.56</v>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E44" s="3" t="inlineStr">
         <is>
           <t>717/717</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F44" s="3" t="inlineStr">
         <is>
           <t>NODE_27_length_3051_cov_11.101231</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="G44" s="3" t="inlineStr">
         <is>
           <t>1749..2465</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="H44" s="3" t="inlineStr">
         <is>
           <t>FR821780</t>
         </is>
       </c>
-      <c r="I44" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
+      <c r="I44" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
         <is>
           <t>NODE_27_length_3051_cov_11.101231:1749..2465:rep21_20_p020(pLGA251)_FR821780:94.560669</t>
         </is>
       </c>
-      <c r="K44" s="2" t="inlineStr">
+      <c r="K44" s="3" t="inlineStr">
         <is>
           <t>1..717</t>
         </is>
@@ -4958,48 +4958,48 @@
           <t>Q0003_BC00104</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B45" s="3" t="inlineStr">
         <is>
           <t>Rep_trans</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
+      <c r="C45" s="3" t="inlineStr">
         <is>
           <t>rep7c</t>
         </is>
       </c>
-      <c r="D45" s="2" t="n">
+      <c r="D45" s="3" t="n">
         <v>98.54000000000001</v>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E45" s="3" t="inlineStr">
         <is>
           <t>821/821</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F45" s="3" t="inlineStr">
         <is>
           <t>NODE_5_length_268507_cov_11.979052</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr">
+      <c r="G45" s="3" t="inlineStr">
         <is>
           <t>135111..135930</t>
         </is>
       </c>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="H45" s="3" t="inlineStr">
         <is>
           <t>BX571857</t>
         </is>
       </c>
-      <c r="I45" s="2" t="n">
+      <c r="I45" s="3" t="n">
         <v>99.88</v>
       </c>
-      <c r="J45" s="2" t="inlineStr">
+      <c r="J45" s="3" t="inlineStr">
         <is>
           <t>NODE_5_length_268507_cov_11.979052:135111..135930:rep7c_1_rep(MSSA476)_BX571857:98.418345</t>
         </is>
       </c>
-      <c r="K45" s="2" t="inlineStr">
+      <c r="K45" s="3" t="inlineStr">
         <is>
           <t>1..821</t>
         </is>
@@ -5170,48 +5170,48 @@
           <t>Q0003_BC00410-2</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B49" s="3" t="inlineStr">
         <is>
           <t>Inc18</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
+      <c r="C49" s="3" t="inlineStr">
         <is>
           <t>repUS5</t>
         </is>
       </c>
-      <c r="D49" s="2" t="n">
+      <c r="D49" s="3" t="n">
         <v>99.3</v>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E49" s="3" t="inlineStr">
         <is>
           <t>1575/1575</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F49" s="3" t="inlineStr">
         <is>
           <t>NODE_9_length_35814_cov_51.069353</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr">
+      <c r="G49" s="3" t="inlineStr">
         <is>
           <t>1700..3274</t>
         </is>
       </c>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="H49" s="3" t="inlineStr">
         <is>
           <t>NC003265</t>
         </is>
       </c>
-      <c r="I49" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="J49" s="2" t="inlineStr">
+      <c r="I49" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
         <is>
           <t>NODE_9_length_35814_cov_51.069353:1700..3274:repUS5_1_CDS20(pETB)_NC003265:99.301587</t>
         </is>
       </c>
-      <c r="K49" s="2" t="inlineStr">
+      <c r="K49" s="3" t="inlineStr">
         <is>
           <t>1..1575</t>
         </is>
@@ -5276,48 +5276,48 @@
           <t>Q0003_BC00410-2</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B51" s="3" t="inlineStr">
         <is>
           <t>Rep1</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
+      <c r="C51" s="3" t="inlineStr">
         <is>
           <t>rep13</t>
         </is>
       </c>
-      <c r="D51" s="2" t="n">
+      <c r="D51" s="3" t="n">
         <v>97.40000000000001</v>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E51" s="3" t="inlineStr">
         <is>
           <t>846/846</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F51" s="3" t="inlineStr">
         <is>
           <t>NODE_12_length_2725_cov_2093.025019</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr">
+      <c r="G51" s="3" t="inlineStr">
         <is>
           <t>616..1461</t>
         </is>
       </c>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="H51" s="3" t="inlineStr">
         <is>
           <t>EU170347</t>
         </is>
       </c>
-      <c r="I51" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="J51" s="2" t="inlineStr">
+      <c r="I51" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
         <is>
           <t>NODE_12_length_2725_cov_2093.025019:616..1461:rep13_4_rep(pKH13)_EU170347:97.399527</t>
         </is>
       </c>
-      <c r="K51" s="2" t="inlineStr">
+      <c r="K51" s="3" t="inlineStr">
         <is>
           <t>1..846</t>
         </is>
@@ -5329,48 +5329,48 @@
           <t>Q0003_BC00410-2</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B52" s="3" t="inlineStr">
         <is>
           <t>Rep_trans</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
+      <c r="C52" s="3" t="inlineStr">
         <is>
           <t>rep7c</t>
         </is>
       </c>
-      <c r="D52" s="2" t="n">
+      <c r="D52" s="3" t="n">
         <v>99.63</v>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E52" s="3" t="inlineStr">
         <is>
           <t>821/821</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F52" s="3" t="inlineStr">
         <is>
           <t>NODE_2_length_635514_cov_10.376311</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr">
+      <c r="G52" s="3" t="inlineStr">
         <is>
           <t>366793..367613</t>
         </is>
       </c>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="H52" s="3" t="inlineStr">
         <is>
           <t>BX571857</t>
         </is>
       </c>
-      <c r="I52" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="J52" s="2" t="inlineStr">
+      <c r="I52" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
         <is>
           <t>NODE_2_length_635514_cov_10.376311:366793..367613:rep7c_1_rep(MSSA476)_BX571857:99.634592</t>
         </is>
       </c>
-      <c r="K52" s="2" t="inlineStr">
+      <c r="K52" s="3" t="inlineStr">
         <is>
           <t>1..821</t>
         </is>
@@ -5382,48 +5382,48 @@
           <t>Q0003_MC0026</t>
         </is>
       </c>
-      <c r="B53" s="3" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>Rep1</t>
         </is>
       </c>
-      <c r="C53" s="3" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
         <is>
           <t>rep21</t>
         </is>
       </c>
-      <c r="D53" s="3" t="n">
+      <c r="D53" s="2" t="n">
         <v>90.38</v>
       </c>
-      <c r="E53" s="3" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>988/1005</t>
         </is>
       </c>
-      <c r="F53" s="3" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>NODE_28_length_3640_cov_202.057785</t>
         </is>
       </c>
-      <c r="G53" s="3" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr">
         <is>
           <t>882..1869</t>
         </is>
       </c>
-      <c r="H53" s="3" t="inlineStr">
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>AM184102</t>
         </is>
       </c>
-      <c r="I53" s="3" t="n">
+      <c r="I53" s="2" t="n">
         <v>98.31</v>
       </c>
-      <c r="J53" s="3" t="inlineStr">
+      <c r="J53" s="2" t="inlineStr">
         <is>
           <t>NODE_28_length_3640_cov_202.057785:882..1869:rep21_27_rep(pLNU4)_AM184102:88.855721</t>
         </is>
       </c>
-      <c r="K53" s="3" t="inlineStr">
+      <c r="K53" s="2" t="inlineStr">
         <is>
           <t>1..988</t>
         </is>
@@ -5488,48 +5488,48 @@
           <t>Q0003_MC0026</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B55" s="3" t="inlineStr">
         <is>
           <t>Rep_trans</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
+      <c r="C55" s="3" t="inlineStr">
         <is>
           <t>rep7a</t>
         </is>
       </c>
-      <c r="D55" s="2" t="n">
+      <c r="D55" s="3" t="n">
         <v>99.89</v>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E55" s="3" t="inlineStr">
         <is>
           <t>945/945</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F55" s="3" t="inlineStr">
         <is>
           <t>NODE_26_length_4524_cov_160.656811</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr">
+      <c r="G55" s="3" t="inlineStr">
         <is>
           <t>588..1532</t>
         </is>
       </c>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="H55" s="3" t="inlineStr">
         <is>
           <t>NC005564</t>
         </is>
       </c>
-      <c r="I55" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="J55" s="2" t="inlineStr">
+      <c r="I55" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
         <is>
           <t>NODE_26_length_4524_cov_160.656811:588..1532:rep7a_17_CDS4(pS194)_NC005564:99.894180</t>
         </is>
       </c>
-      <c r="K55" s="2" t="inlineStr">
+      <c r="K55" s="3" t="inlineStr">
         <is>
           <t>1..945</t>
         </is>
@@ -5541,48 +5541,48 @@
           <t>Q0003_BC00108</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B56" s="3" t="inlineStr">
         <is>
           <t>Rep1</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
+      <c r="C56" s="3" t="inlineStr">
         <is>
           <t>rep21</t>
         </is>
       </c>
-      <c r="D56" s="2" t="n">
+      <c r="D56" s="3" t="n">
         <v>99.90000000000001</v>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E56" s="3" t="inlineStr">
         <is>
           <t>996/996</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F56" s="3" t="inlineStr">
         <is>
           <t>NODE_28_length_3640_cov_1107.717051</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr">
+      <c r="G56" s="3" t="inlineStr">
         <is>
           <t>1710..2705</t>
         </is>
       </c>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="H56" s="3" t="inlineStr">
         <is>
           <t>plasmid2)NC022227</t>
         </is>
       </c>
-      <c r="I56" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
+      <c r="I56" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
         <is>
           <t>NODE_28_length_3640_cov_1107.717051:1710..2705:rep21_24_rep(CN1_plasmid2)_NC_022227:99.899598</t>
         </is>
       </c>
-      <c r="K56" s="2" t="inlineStr">
+      <c r="K56" s="3" t="inlineStr">
         <is>
           <t>1..996</t>
         </is>
@@ -5594,48 +5594,48 @@
           <t>Q0003_BC00108</t>
         </is>
       </c>
-      <c r="B57" s="3" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>Rep_trans</t>
         </is>
       </c>
-      <c r="C57" s="3" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
         <is>
           <t>rep7a</t>
         </is>
       </c>
-      <c r="D57" s="3" t="n">
+      <c r="D57" s="2" t="n">
         <v>92.51000000000001</v>
       </c>
-      <c r="E57" s="3" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>934/936</t>
         </is>
       </c>
-      <c r="F57" s="3" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>NODE_25_length_3920_cov_809.363828</t>
         </is>
       </c>
-      <c r="G57" s="3" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr">
         <is>
           <t>412..1345</t>
         </is>
       </c>
-      <c r="H57" s="3" t="inlineStr">
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>NC010111</t>
         </is>
       </c>
-      <c r="I57" s="3" t="n">
+      <c r="I57" s="2" t="n">
         <v>99.79000000000001</v>
       </c>
-      <c r="J57" s="3" t="inlineStr">
+      <c r="J57" s="2" t="inlineStr">
         <is>
           <t>NODE_25_length_3920_cov_809.363828:412..1345:rep7a_5_repD(pTZ4)_NC010111:92.307692</t>
         </is>
       </c>
-      <c r="K57" s="3" t="inlineStr">
+      <c r="K57" s="2" t="inlineStr">
         <is>
           <t>1..934</t>
         </is>
@@ -5647,48 +5647,48 @@
           <t>R0051_TC00505</t>
         </is>
       </c>
-      <c r="B58" s="3" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>Rep1</t>
         </is>
       </c>
-      <c r="C58" s="3" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
         <is>
           <t>rep21</t>
         </is>
       </c>
-      <c r="D58" s="3" t="n">
+      <c r="D58" s="2" t="n">
         <v>90.38</v>
       </c>
-      <c r="E58" s="3" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>988/1005</t>
         </is>
       </c>
-      <c r="F58" s="3" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>NODE_24_length_3640_cov_4633.460575</t>
         </is>
       </c>
-      <c r="G58" s="3" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr">
         <is>
           <t>794..1781</t>
         </is>
       </c>
-      <c r="H58" s="3" t="inlineStr">
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>AM184102</t>
         </is>
       </c>
-      <c r="I58" s="3" t="n">
+      <c r="I58" s="2" t="n">
         <v>98.31</v>
       </c>
-      <c r="J58" s="3" t="inlineStr">
+      <c r="J58" s="2" t="inlineStr">
         <is>
           <t>NODE_24_length_3640_cov_4633.460575:794..1781:rep21_27_rep(pLNU4)_AM184102:88.855721</t>
         </is>
       </c>
-      <c r="K58" s="3" t="inlineStr">
+      <c r="K58" s="2" t="inlineStr">
         <is>
           <t>1..988</t>
         </is>
@@ -5700,48 +5700,48 @@
           <t>R0051_TC00505</t>
         </is>
       </c>
-      <c r="B59" s="3" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>Rep1</t>
         </is>
       </c>
-      <c r="C59" s="3" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
         <is>
           <t>rep21</t>
         </is>
       </c>
-      <c r="D59" s="3" t="n">
+      <c r="D59" s="2" t="n">
         <v>94.84</v>
       </c>
-      <c r="E59" s="3" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>717/717</t>
         </is>
       </c>
-      <c r="F59" s="3" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>NODE_25_length_2576_cov_20.299714</t>
         </is>
       </c>
-      <c r="G59" s="3" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr">
         <is>
           <t>1520..2236</t>
         </is>
       </c>
-      <c r="H59" s="3" t="inlineStr">
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>FR821780</t>
         </is>
       </c>
-      <c r="I59" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="J59" s="3" t="inlineStr">
+      <c r="I59" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
         <is>
           <t>NODE_25_length_2576_cov_20.299714:1520..2236:rep21_20_p020(pLGA251)_FR821780:94.839609</t>
         </is>
       </c>
-      <c r="K59" s="3" t="inlineStr">
+      <c r="K59" s="2" t="inlineStr">
         <is>
           <t>1..717</t>
         </is>
@@ -5753,48 +5753,48 @@
           <t>R0051_TC00505</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B60" s="3" t="inlineStr">
         <is>
           <t>Rep_trans</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
+      <c r="C60" s="3" t="inlineStr">
         <is>
           <t>rep7c</t>
         </is>
       </c>
-      <c r="D60" s="2" t="n">
+      <c r="D60" s="3" t="n">
         <v>98.54000000000001</v>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E60" s="3" t="inlineStr">
         <is>
           <t>821/821</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F60" s="3" t="inlineStr">
         <is>
           <t>NODE_4_length_277122_cov_30.730042</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr">
+      <c r="G60" s="3" t="inlineStr">
         <is>
           <t>134259..135078</t>
         </is>
       </c>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="H60" s="3" t="inlineStr">
         <is>
           <t>BX571857</t>
         </is>
       </c>
-      <c r="I60" s="2" t="n">
+      <c r="I60" s="3" t="n">
         <v>99.88</v>
       </c>
-      <c r="J60" s="2" t="inlineStr">
+      <c r="J60" s="3" t="inlineStr">
         <is>
           <t>NODE_4_length_277122_cov_30.730042:134259..135078:rep7c_1_rep(MSSA476)_BX571857:98.418345</t>
         </is>
       </c>
-      <c r="K60" s="2" t="inlineStr">
+      <c r="K60" s="3" t="inlineStr">
         <is>
           <t>1..821</t>
         </is>
@@ -5859,48 +5859,48 @@
           <t>Q0003_BC00110</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="B62" s="3" t="inlineStr">
         <is>
           <t>Rep1</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
+      <c r="C62" s="3" t="inlineStr">
         <is>
           <t>rep21</t>
         </is>
       </c>
-      <c r="D62" s="2" t="n">
+      <c r="D62" s="3" t="n">
         <v>99.90000000000001</v>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E62" s="3" t="inlineStr">
         <is>
           <t>996/996</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F62" s="3" t="inlineStr">
         <is>
           <t>NODE_22_length_9138_cov_1352.811897</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr">
+      <c r="G62" s="3" t="inlineStr">
         <is>
           <t>6433..7428</t>
         </is>
       </c>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="H62" s="3" t="inlineStr">
         <is>
           <t>plasmid2)NC022227</t>
         </is>
       </c>
-      <c r="I62" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="J62" s="2" t="inlineStr">
+      <c r="I62" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
         <is>
           <t>NODE_22_length_9138_cov_1352.811897:6433..7428:rep21_24_rep(CN1_plasmid2)_NC_022227:99.899598</t>
         </is>
       </c>
-      <c r="K62" s="2" t="inlineStr">
+      <c r="K62" s="3" t="inlineStr">
         <is>
           <t>1..996</t>
         </is>
@@ -5912,48 +5912,48 @@
           <t>Q0003_BC00110</t>
         </is>
       </c>
-      <c r="B63" s="3" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>Rep_trans</t>
         </is>
       </c>
-      <c r="C63" s="3" t="inlineStr">
+      <c r="C63" s="2" t="inlineStr">
         <is>
           <t>rep7a</t>
         </is>
       </c>
-      <c r="D63" s="3" t="n">
+      <c r="D63" s="2" t="n">
         <v>92.51000000000001</v>
       </c>
-      <c r="E63" s="3" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>934/936</t>
         </is>
       </c>
-      <c r="F63" s="3" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>NODE_27_length_3990_cov_1518.827595</t>
         </is>
       </c>
-      <c r="G63" s="3" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr">
         <is>
           <t>2576..3509</t>
         </is>
       </c>
-      <c r="H63" s="3" t="inlineStr">
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>NC010111</t>
         </is>
       </c>
-      <c r="I63" s="3" t="n">
+      <c r="I63" s="2" t="n">
         <v>99.79000000000001</v>
       </c>
-      <c r="J63" s="3" t="inlineStr">
+      <c r="J63" s="2" t="inlineStr">
         <is>
           <t>NODE_27_length_3990_cov_1518.827595:2576..3509:rep7a_5_repD(pTZ4)_NC010111:92.307692</t>
         </is>
       </c>
-      <c r="K63" s="3" t="inlineStr">
+      <c r="K63" s="2" t="inlineStr">
         <is>
           <t>1..934</t>
         </is>
@@ -6071,48 +6071,48 @@
           <t>R0047_TH0405</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="B66" s="3" t="inlineStr">
         <is>
           <t>RepA_N</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
+      <c r="C66" s="3" t="inlineStr">
         <is>
           <t>rep24b</t>
         </is>
       </c>
-      <c r="D66" s="2" t="n">
+      <c r="D66" s="3" t="n">
         <v>99.90000000000001</v>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E66" s="3" t="inlineStr">
         <is>
           <t>984/984</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F66" s="3" t="inlineStr">
         <is>
           <t>NODE_27_length_35583_cov_14.364818</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr">
+      <c r="G66" s="3" t="inlineStr">
         <is>
           <t>30208..31191</t>
         </is>
       </c>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="H66" s="3" t="inlineStr">
         <is>
           <t>GQ900391</t>
         </is>
       </c>
-      <c r="I66" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="J66" s="2" t="inlineStr">
+      <c r="I66" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
         <is>
           <t>NODE_27_length_35583_cov_14.364818:30208..31191:rep24b_1_rep(pWBG749)_GQ900391:99.898374</t>
         </is>
       </c>
-      <c r="K66" s="2" t="inlineStr">
+      <c r="K66" s="3" t="inlineStr">
         <is>
           <t>1..984</t>
         </is>
@@ -6177,48 +6177,48 @@
           <t>Q0003_MC00211</t>
         </is>
       </c>
-      <c r="B68" s="3" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>Rep1</t>
         </is>
       </c>
-      <c r="C68" s="3" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr">
         <is>
           <t>rep21</t>
         </is>
       </c>
-      <c r="D68" s="3" t="n">
+      <c r="D68" s="2" t="n">
         <v>90.08</v>
       </c>
-      <c r="E68" s="3" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>605/1005</t>
         </is>
       </c>
-      <c r="F68" s="3" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>NODE_17_length_3640_cov_3684.020780</t>
         </is>
       </c>
-      <c r="G68" s="3" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr">
         <is>
           <t>3027..3631</t>
         </is>
       </c>
-      <c r="H68" s="3" t="inlineStr">
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>AM184102</t>
         </is>
       </c>
-      <c r="I68" s="3" t="n">
+      <c r="I68" s="2" t="n">
         <v>60.2</v>
       </c>
-      <c r="J68" s="3" t="inlineStr">
+      <c r="J68" s="2" t="inlineStr">
         <is>
           <t>NODE_17_length_3640_cov_3684.020780:3027..3631:rep21_27_rep(pLNU4)_AM184102:54.228856</t>
         </is>
       </c>
-      <c r="K68" s="3" t="inlineStr">
+      <c r="K68" s="2" t="inlineStr">
         <is>
           <t>1..605</t>
         </is>
@@ -6495,48 +6495,48 @@
           <t>Q0003_BC00416</t>
         </is>
       </c>
-      <c r="B74" s="3" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>Rep1</t>
         </is>
       </c>
-      <c r="C74" s="3" t="inlineStr">
+      <c r="C74" s="2" t="inlineStr">
         <is>
           <t>rep21</t>
         </is>
       </c>
-      <c r="D74" s="3" t="n">
+      <c r="D74" s="2" t="n">
         <v>93.09999999999999</v>
       </c>
-      <c r="E74" s="3" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>783/1005</t>
         </is>
       </c>
-      <c r="F74" s="3" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>NODE_19_length_6648_cov_205.926085</t>
         </is>
       </c>
-      <c r="G74" s="3" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr">
         <is>
           <t>1675..2457</t>
         </is>
       </c>
-      <c r="H74" s="3" t="inlineStr">
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>AM399081</t>
         </is>
       </c>
-      <c r="I74" s="3" t="n">
+      <c r="I74" s="2" t="n">
         <v>77.91</v>
       </c>
-      <c r="J74" s="3" t="inlineStr">
+      <c r="J74" s="2" t="inlineStr">
         <is>
           <t>NODE_19_length_6648_cov_205.926085:1675..2457:rep21_19_rep(pLNU7)_AM399081:72.537313</t>
         </is>
       </c>
-      <c r="K74" s="3" t="inlineStr">
+      <c r="K74" s="2" t="inlineStr">
         <is>
           <t>223..1005</t>
         </is>
@@ -6548,48 +6548,48 @@
           <t>Q0003_BC00416</t>
         </is>
       </c>
-      <c r="B75" s="3" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
         <is>
           <t>Rep1</t>
         </is>
       </c>
-      <c r="C75" s="3" t="inlineStr">
+      <c r="C75" s="2" t="inlineStr">
         <is>
           <t>rep21</t>
         </is>
       </c>
-      <c r="D75" s="3" t="n">
+      <c r="D75" s="2" t="n">
         <v>96.51000000000001</v>
       </c>
-      <c r="E75" s="3" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>717/717</t>
         </is>
       </c>
-      <c r="F75" s="3" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>NODE_19_length_6648_cov_205.926085</t>
         </is>
       </c>
-      <c r="G75" s="3" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr">
         <is>
           <t>5506..6222</t>
         </is>
       </c>
-      <c r="H75" s="3" t="inlineStr">
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>FR821780</t>
         </is>
       </c>
-      <c r="I75" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="J75" s="3" t="inlineStr">
+      <c r="I75" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
         <is>
           <t>NODE_19_length_6648_cov_205.926085:5506..6222:rep21_20_p020(pLGA251)_FR821780:96.513250</t>
         </is>
       </c>
-      <c r="K75" s="3" t="inlineStr">
+      <c r="K75" s="2" t="inlineStr">
         <is>
           <t>1..717</t>
         </is>
@@ -6654,48 +6654,48 @@
           <t>Q0003_BC00201</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="B77" s="3" t="inlineStr">
         <is>
           <t>Rep1</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
+      <c r="C77" s="3" t="inlineStr">
         <is>
           <t>rep21</t>
         </is>
       </c>
-      <c r="D77" s="2" t="n">
+      <c r="D77" s="3" t="n">
         <v>94.56</v>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E77" s="3" t="inlineStr">
         <is>
           <t>717/717</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F77" s="3" t="inlineStr">
         <is>
           <t>NODE_22_length_2765_cov_11.448825</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr">
+      <c r="G77" s="3" t="inlineStr">
         <is>
           <t>1749..2465</t>
         </is>
       </c>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="H77" s="3" t="inlineStr">
         <is>
           <t>FR821780</t>
         </is>
       </c>
-      <c r="I77" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="J77" s="2" t="inlineStr">
+      <c r="I77" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="J77" s="3" t="inlineStr">
         <is>
           <t>NODE_22_length_2765_cov_11.448825:1749..2465:rep21_20_p020(pLGA251)_FR821780:94.560669</t>
         </is>
       </c>
-      <c r="K77" s="2" t="inlineStr">
+      <c r="K77" s="3" t="inlineStr">
         <is>
           <t>1..717</t>
         </is>
@@ -6707,48 +6707,48 @@
           <t>Q0003_BC00201</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
+      <c r="B78" s="3" t="inlineStr">
         <is>
           <t>Rep_trans</t>
         </is>
       </c>
-      <c r="C78" s="2" t="inlineStr">
+      <c r="C78" s="3" t="inlineStr">
         <is>
           <t>rep7c</t>
         </is>
       </c>
-      <c r="D78" s="2" t="n">
+      <c r="D78" s="3" t="n">
         <v>98.54000000000001</v>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E78" s="3" t="inlineStr">
         <is>
           <t>821/821</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F78" s="3" t="inlineStr">
         <is>
           <t>NODE_4_length_267825_cov_30.304111</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr">
+      <c r="G78" s="3" t="inlineStr">
         <is>
           <t>132633..133452</t>
         </is>
       </c>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="H78" s="3" t="inlineStr">
         <is>
           <t>BX571857</t>
         </is>
       </c>
-      <c r="I78" s="2" t="n">
+      <c r="I78" s="3" t="n">
         <v>99.88</v>
       </c>
-      <c r="J78" s="2" t="inlineStr">
+      <c r="J78" s="3" t="inlineStr">
         <is>
           <t>NODE_4_length_267825_cov_30.304111:132633..133452:rep7c_1_rep(MSSA476)_BX571857:98.418345</t>
         </is>
       </c>
-      <c r="K78" s="2" t="inlineStr">
+      <c r="K78" s="3" t="inlineStr">
         <is>
           <t>1..821</t>
         </is>
@@ -6866,48 +6866,48 @@
           <t>Q0003_BC00107</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
+      <c r="B81" s="3" t="inlineStr">
         <is>
           <t>Rep1</t>
         </is>
       </c>
-      <c r="C81" s="2" t="inlineStr">
+      <c r="C81" s="3" t="inlineStr">
         <is>
           <t>rep21</t>
         </is>
       </c>
-      <c r="D81" s="2" t="n">
+      <c r="D81" s="3" t="n">
         <v>94.56</v>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E81" s="3" t="inlineStr">
         <is>
           <t>717/717</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F81" s="3" t="inlineStr">
         <is>
           <t>NODE_25_length_2765_cov_14.235027</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr">
+      <c r="G81" s="3" t="inlineStr">
         <is>
           <t>301..1017</t>
         </is>
       </c>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="H81" s="3" t="inlineStr">
         <is>
           <t>FR821780</t>
         </is>
       </c>
-      <c r="I81" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="J81" s="2" t="inlineStr">
+      <c r="I81" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="J81" s="3" t="inlineStr">
         <is>
           <t>NODE_25_length_2765_cov_14.235027:301..1017:rep21_20_p020(pLGA251)_FR821780:94.560669</t>
         </is>
       </c>
-      <c r="K81" s="2" t="inlineStr">
+      <c r="K81" s="3" t="inlineStr">
         <is>
           <t>1..717</t>
         </is>
@@ -6919,48 +6919,48 @@
           <t>Q0003_BC00107</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
+      <c r="B82" s="3" t="inlineStr">
         <is>
           <t>Rep_trans</t>
         </is>
       </c>
-      <c r="C82" s="2" t="inlineStr">
+      <c r="C82" s="3" t="inlineStr">
         <is>
           <t>rep7c</t>
         </is>
       </c>
-      <c r="D82" s="2" t="n">
+      <c r="D82" s="3" t="n">
         <v>98.54000000000001</v>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E82" s="3" t="inlineStr">
         <is>
           <t>821/821</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F82" s="3" t="inlineStr">
         <is>
           <t>NODE_4_length_268507_cov_27.116302</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr">
+      <c r="G82" s="3" t="inlineStr">
         <is>
           <t>132578..133397</t>
         </is>
       </c>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="H82" s="3" t="inlineStr">
         <is>
           <t>BX571857</t>
         </is>
       </c>
-      <c r="I82" s="2" t="n">
+      <c r="I82" s="3" t="n">
         <v>99.88</v>
       </c>
-      <c r="J82" s="2" t="inlineStr">
+      <c r="J82" s="3" t="inlineStr">
         <is>
           <t>NODE_4_length_268507_cov_27.116302:132578..133397:rep7c_1_rep(MSSA476)_BX571857:98.418345</t>
         </is>
       </c>
-      <c r="K82" s="2" t="inlineStr">
+      <c r="K82" s="3" t="inlineStr">
         <is>
           <t>1..821</t>
         </is>
@@ -7078,48 +7078,48 @@
           <t>R0051_HK2002</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
+      <c r="B85" s="3" t="inlineStr">
         <is>
           <t>Rep3</t>
         </is>
       </c>
-      <c r="C85" s="2" t="inlineStr">
+      <c r="C85" s="3" t="inlineStr">
         <is>
           <t>rep5c</t>
         </is>
       </c>
-      <c r="D85" s="2" t="n">
+      <c r="D85" s="3" t="n">
         <v>91.03</v>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E85" s="3" t="inlineStr">
         <is>
           <t>858/858</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F85" s="3" t="inlineStr">
         <is>
           <t>NODE_68_length_5302_cov_242.990338</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr">
+      <c r="G85" s="3" t="inlineStr">
         <is>
           <t>437..1294</t>
         </is>
       </c>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="H85" s="3" t="inlineStr">
         <is>
           <t>AF447813</t>
         </is>
       </c>
-      <c r="I85" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="J85" s="2" t="inlineStr">
+      <c r="I85" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="J85" s="3" t="inlineStr">
         <is>
           <t>NODE_68_length_5302_cov_242.990338:437..1294:rep5c_1_rep(pRJ9)_AF447813:91.025641</t>
         </is>
       </c>
-      <c r="K85" s="2" t="inlineStr">
+      <c r="K85" s="3" t="inlineStr">
         <is>
           <t>1..858</t>
         </is>
@@ -7237,48 +7237,48 @@
           <t>R0051_TC00402</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
+      <c r="B88" s="3" t="inlineStr">
         <is>
           <t>RepA_N</t>
         </is>
       </c>
-      <c r="C88" s="2" t="inlineStr">
+      <c r="C88" s="3" t="inlineStr">
         <is>
           <t>rep20</t>
         </is>
       </c>
-      <c r="D88" s="2" t="n">
+      <c r="D88" s="3" t="n">
         <v>99.89</v>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E88" s="3" t="inlineStr">
         <is>
           <t>899/899</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F88" s="3" t="inlineStr">
         <is>
           <t>NODE_29_length_21479_cov_50.856220</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr">
+      <c r="G88" s="3" t="inlineStr">
         <is>
           <t>1216..2114</t>
         </is>
       </c>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="H88" s="3" t="inlineStr">
         <is>
           <t>NC013334</t>
         </is>
       </c>
-      <c r="I88" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="J88" s="2" t="inlineStr">
+      <c r="I88" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="J88" s="3" t="inlineStr">
         <is>
           <t>NODE_29_length_21479_cov_50.856220:1216..2114:rep20_10_repA(SAP057A)_NC013334:99.888765</t>
         </is>
       </c>
-      <c r="K88" s="2" t="inlineStr">
+      <c r="K88" s="3" t="inlineStr">
         <is>
           <t>1..899</t>
         </is>
@@ -7502,48 +7502,48 @@
           <t>Q0003_BC00304</t>
         </is>
       </c>
-      <c r="B93" s="3" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
         <is>
           <t>Rep1</t>
         </is>
       </c>
-      <c r="C93" s="3" t="inlineStr">
+      <c r="C93" s="2" t="inlineStr">
         <is>
           <t>rep21</t>
         </is>
       </c>
-      <c r="D93" s="3" t="n">
+      <c r="D93" s="2" t="n">
         <v>90.38</v>
       </c>
-      <c r="E93" s="3" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>988/1005</t>
         </is>
       </c>
-      <c r="F93" s="3" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t>NODE_15_length_3640_cov_2230.854256</t>
         </is>
       </c>
-      <c r="G93" s="3" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr">
         <is>
           <t>1103..2090</t>
         </is>
       </c>
-      <c r="H93" s="3" t="inlineStr">
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>AM184102</t>
         </is>
       </c>
-      <c r="I93" s="3" t="n">
+      <c r="I93" s="2" t="n">
         <v>98.31</v>
       </c>
-      <c r="J93" s="3" t="inlineStr">
+      <c r="J93" s="2" t="inlineStr">
         <is>
           <t>NODE_15_length_3640_cov_2230.854256:1103..2090:rep21_27_rep(pLNU4)_AM184102:88.855721</t>
         </is>
       </c>
-      <c r="K93" s="3" t="inlineStr">
+      <c r="K93" s="2" t="inlineStr">
         <is>
           <t>1..988</t>
         </is>
@@ -7555,48 +7555,48 @@
           <t>Q0003_BC00304</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
+      <c r="B94" s="3" t="inlineStr">
         <is>
           <t>Rep_trans</t>
         </is>
       </c>
-      <c r="C94" s="2" t="inlineStr">
+      <c r="C94" s="3" t="inlineStr">
         <is>
           <t>rep7a</t>
         </is>
       </c>
-      <c r="D94" s="2" t="n">
+      <c r="D94" s="3" t="n">
         <v>99.89</v>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E94" s="3" t="inlineStr">
         <is>
           <t>945/945</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F94" s="3" t="inlineStr">
         <is>
           <t>NODE_14_length_4524_cov_684.118035</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr">
+      <c r="G94" s="3" t="inlineStr">
         <is>
           <t>3079..4023</t>
         </is>
       </c>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="H94" s="3" t="inlineStr">
         <is>
           <t>NC005564</t>
         </is>
       </c>
-      <c r="I94" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="J94" s="2" t="inlineStr">
+      <c r="I94" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="J94" s="3" t="inlineStr">
         <is>
           <t>NODE_14_length_4524_cov_684.118035:3079..4023:rep7a_17_CDS4(pS194)_NC005564:99.894180</t>
         </is>
       </c>
-      <c r="K94" s="2" t="inlineStr">
+      <c r="K94" s="3" t="inlineStr">
         <is>
           <t>1..945</t>
         </is>
@@ -7608,48 +7608,48 @@
           <t>Q0003_BC00406</t>
         </is>
       </c>
-      <c r="B95" s="3" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
         <is>
           <t>Rep1</t>
         </is>
       </c>
-      <c r="C95" s="3" t="inlineStr">
+      <c r="C95" s="2" t="inlineStr">
         <is>
           <t>rep21</t>
         </is>
       </c>
-      <c r="D95" s="3" t="n">
+      <c r="D95" s="2" t="n">
         <v>93.27</v>
       </c>
-      <c r="E95" s="3" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>891/950</t>
         </is>
       </c>
-      <c r="F95" s="3" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>NODE_33_length_5960_cov_8142.030002</t>
         </is>
       </c>
-      <c r="G95" s="3" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr">
         <is>
           <t>27..917</t>
         </is>
       </c>
-      <c r="H95" s="3" t="inlineStr">
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>AF051917</t>
         </is>
       </c>
-      <c r="I95" s="3" t="n">
+      <c r="I95" s="2" t="n">
         <v>93.79000000000001</v>
       </c>
-      <c r="J95" s="3" t="inlineStr">
+      <c r="J95" s="2" t="inlineStr">
         <is>
           <t>NODE_33_length_5960_cov_8142.030002:27..917:rep21_4_repRC(pSK41)_AF051917:87.473684</t>
         </is>
       </c>
-      <c r="K95" s="3" t="inlineStr">
+      <c r="K95" s="2" t="inlineStr">
         <is>
           <t>1..891</t>
         </is>
@@ -7661,48 +7661,48 @@
           <t>Q0003_BC00406</t>
         </is>
       </c>
-      <c r="B96" s="3" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
         <is>
           <t>Rep1</t>
         </is>
       </c>
-      <c r="C96" s="3" t="inlineStr">
+      <c r="C96" s="2" t="inlineStr">
         <is>
           <t>rep21</t>
         </is>
       </c>
-      <c r="D96" s="3" t="n">
+      <c r="D96" s="2" t="n">
         <v>93.27</v>
       </c>
-      <c r="E96" s="3" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>891/927</t>
         </is>
       </c>
-      <c r="F96" s="3" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>NODE_33_length_5960_cov_8142.030002</t>
         </is>
       </c>
-      <c r="G96" s="3" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr">
         <is>
           <t>27..917</t>
         </is>
       </c>
-      <c r="H96" s="3" t="inlineStr">
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>FM207042</t>
         </is>
       </c>
-      <c r="I96" s="3" t="n">
+      <c r="I96" s="2" t="n">
         <v>96.12</v>
       </c>
-      <c r="J96" s="3" t="inlineStr">
+      <c r="J96" s="2" t="inlineStr">
         <is>
           <t>NODE_33_length_5960_cov_8142.030002:27..917:rep21_5_repRC(pGO1)_FM207042:89.644013</t>
         </is>
       </c>
-      <c r="K96" s="3" t="inlineStr">
+      <c r="K96" s="2" t="inlineStr">
         <is>
           <t>37..927</t>
         </is>
@@ -7714,48 +7714,48 @@
           <t>Q0003_BC00406</t>
         </is>
       </c>
-      <c r="B97" s="3" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
         <is>
           <t>Rep1</t>
         </is>
       </c>
-      <c r="C97" s="3" t="inlineStr">
+      <c r="C97" s="2" t="inlineStr">
         <is>
           <t>rep21</t>
         </is>
       </c>
-      <c r="D97" s="3" t="n">
+      <c r="D97" s="2" t="n">
         <v>97.69</v>
       </c>
-      <c r="E97" s="3" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>996/996</t>
         </is>
       </c>
-      <c r="F97" s="3" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>NODE_33_length_5960_cov_8142.030002</t>
         </is>
       </c>
-      <c r="G97" s="3" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr">
         <is>
           <t>2129..3124</t>
         </is>
       </c>
-      <c r="H97" s="3" t="inlineStr">
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>plasmid2)NC022227</t>
         </is>
       </c>
-      <c r="I97" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="J97" s="3" t="inlineStr">
+      <c r="I97" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
         <is>
           <t>NODE_33_length_5960_cov_8142.030002:2129..3124:rep21_24_rep(CN1_plasmid2)_NC_022227:97.690763</t>
         </is>
       </c>
-      <c r="K97" s="3" t="inlineStr">
+      <c r="K97" s="2" t="inlineStr">
         <is>
           <t>1..996</t>
         </is>
@@ -7873,48 +7873,48 @@
           <t>R0047_DABST013</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
+      <c r="B100" s="3" t="inlineStr">
         <is>
           <t>RepA_N</t>
         </is>
       </c>
-      <c r="C100" s="2" t="inlineStr">
+      <c r="C100" s="3" t="inlineStr">
         <is>
           <t>rep20</t>
         </is>
       </c>
-      <c r="D100" s="2" t="n">
+      <c r="D100" s="3" t="n">
         <v>99.89</v>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E100" s="3" t="inlineStr">
         <is>
           <t>899/899</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F100" s="3" t="inlineStr">
         <is>
           <t>NODE_35_length_21480_cov_6.804852</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr">
+      <c r="G100" s="3" t="inlineStr">
         <is>
           <t>1217..2115</t>
         </is>
       </c>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="H100" s="3" t="inlineStr">
         <is>
           <t>NC013334</t>
         </is>
       </c>
-      <c r="I100" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="J100" s="2" t="inlineStr">
+      <c r="I100" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="J100" s="3" t="inlineStr">
         <is>
           <t>NODE_35_length_21480_cov_6.804852:1217..2115:rep20_10_repA(SAP057A)_NC013334:99.888765</t>
         </is>
       </c>
-      <c r="K100" s="2" t="inlineStr">
+      <c r="K100" s="3" t="inlineStr">
         <is>
           <t>1..899</t>
         </is>
@@ -8032,48 +8032,48 @@
           <t>Q0003_MC00115-2</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
+      <c r="B103" s="3" t="inlineStr">
         <is>
           <t>Rep1</t>
         </is>
       </c>
-      <c r="C103" s="2" t="inlineStr">
+      <c r="C103" s="3" t="inlineStr">
         <is>
           <t>rep21</t>
         </is>
       </c>
-      <c r="D103" s="2" t="n">
+      <c r="D103" s="3" t="n">
         <v>94.7</v>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E103" s="3" t="inlineStr">
         <is>
           <t>717/717</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F103" s="3" t="inlineStr">
         <is>
           <t>NODE_18_length_2423_cov_14.526568</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr">
+      <c r="G103" s="3" t="inlineStr">
         <is>
           <t>1364..2080</t>
         </is>
       </c>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="H103" s="3" t="inlineStr">
         <is>
           <t>FR821780</t>
         </is>
       </c>
-      <c r="I103" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="J103" s="2" t="inlineStr">
+      <c r="I103" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="J103" s="3" t="inlineStr">
         <is>
           <t>NODE_18_length_2423_cov_14.526568:1364..2080:rep21_20_p020(pLGA251)_FR821780:94.700139</t>
         </is>
       </c>
-      <c r="K103" s="2" t="inlineStr">
+      <c r="K103" s="3" t="inlineStr">
         <is>
           <t>1..717</t>
         </is>
@@ -8509,48 +8509,48 @@
           <t>R0051_TC00219</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
+      <c r="B112" s="3" t="inlineStr">
         <is>
           <t>Rep1</t>
         </is>
       </c>
-      <c r="C112" s="2" t="inlineStr">
+      <c r="C112" s="3" t="inlineStr">
         <is>
           <t>rep21</t>
         </is>
       </c>
-      <c r="D112" s="2" t="n">
+      <c r="D112" s="3" t="n">
         <v>94.56</v>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E112" s="3" t="inlineStr">
         <is>
           <t>717/717</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F112" s="3" t="inlineStr">
         <is>
           <t>NODE_19_length_19911_cov_17.969774</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr">
+      <c r="G112" s="3" t="inlineStr">
         <is>
           <t>1749..2465</t>
         </is>
       </c>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="H112" s="3" t="inlineStr">
         <is>
           <t>FR821780</t>
         </is>
       </c>
-      <c r="I112" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="J112" s="2" t="inlineStr">
+      <c r="I112" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="J112" s="3" t="inlineStr">
         <is>
           <t>NODE_19_length_19911_cov_17.969774:1749..2465:rep21_20_p020(pLGA251)_FR821780:94.560669</t>
         </is>
       </c>
-      <c r="K112" s="2" t="inlineStr">
+      <c r="K112" s="3" t="inlineStr">
         <is>
           <t>1..717</t>
         </is>
@@ -8562,48 +8562,48 @@
           <t>R0051_TC00219</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
+      <c r="B113" s="3" t="inlineStr">
         <is>
           <t>Rep1</t>
         </is>
       </c>
-      <c r="C113" s="2" t="inlineStr">
+      <c r="C113" s="3" t="inlineStr">
         <is>
           <t>rep21</t>
         </is>
       </c>
-      <c r="D113" s="2" t="n">
+      <c r="D113" s="3" t="n">
         <v>99.90000000000001</v>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E113" s="3" t="inlineStr">
         <is>
           <t>996/996</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="F113" s="3" t="inlineStr">
         <is>
           <t>NODE_21_length_6682_cov_10.520519</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr">
+      <c r="G113" s="3" t="inlineStr">
         <is>
           <t>2778..3773</t>
         </is>
       </c>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="H113" s="3" t="inlineStr">
         <is>
           <t>plasmid2)NC022227</t>
         </is>
       </c>
-      <c r="I113" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="J113" s="2" t="inlineStr">
+      <c r="I113" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="J113" s="3" t="inlineStr">
         <is>
           <t>NODE_21_length_6682_cov_10.520519:2778..3773:rep21_24_rep(CN1_plasmid2)_NC_022227:99.899598</t>
         </is>
       </c>
-      <c r="K113" s="2" t="inlineStr">
+      <c r="K113" s="3" t="inlineStr">
         <is>
           <t>1..996</t>
         </is>
@@ -8615,48 +8615,48 @@
           <t>R0051_TC00219</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
+      <c r="B114" s="3" t="inlineStr">
         <is>
           <t>Rep_trans</t>
         </is>
       </c>
-      <c r="C114" s="2" t="inlineStr">
+      <c r="C114" s="3" t="inlineStr">
         <is>
           <t>rep7c</t>
         </is>
       </c>
-      <c r="D114" s="2" t="n">
+      <c r="D114" s="3" t="n">
         <v>98.54000000000001</v>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E114" s="3" t="inlineStr">
         <is>
           <t>821/821</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="F114" s="3" t="inlineStr">
         <is>
           <t>NODE_5_length_268541_cov_27.508025</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr">
+      <c r="G114" s="3" t="inlineStr">
         <is>
           <t>135145..135964</t>
         </is>
       </c>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="H114" s="3" t="inlineStr">
         <is>
           <t>BX571857</t>
         </is>
       </c>
-      <c r="I114" s="2" t="n">
+      <c r="I114" s="3" t="n">
         <v>99.88</v>
       </c>
-      <c r="J114" s="2" t="inlineStr">
+      <c r="J114" s="3" t="inlineStr">
         <is>
           <t>NODE_5_length_268541_cov_27.508025:135145..135964:rep7c_1_rep(MSSA476)_BX571857:98.418345</t>
         </is>
       </c>
-      <c r="K114" s="2" t="inlineStr">
+      <c r="K114" s="3" t="inlineStr">
         <is>
           <t>1..821</t>
         </is>
@@ -8721,48 +8721,48 @@
           <t>Q0003_MC00114-1</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
+      <c r="B116" s="3" t="inlineStr">
         <is>
           <t>Rep1</t>
         </is>
       </c>
-      <c r="C116" s="2" t="inlineStr">
+      <c r="C116" s="3" t="inlineStr">
         <is>
           <t>rep21</t>
         </is>
       </c>
-      <c r="D116" s="2" t="n">
+      <c r="D116" s="3" t="n">
         <v>94.7</v>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E116" s="3" t="inlineStr">
         <is>
           <t>717/717</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr">
+      <c r="F116" s="3" t="inlineStr">
         <is>
           <t>NODE_37_length_4617_cov_2.071269</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr">
+      <c r="G116" s="3" t="inlineStr">
         <is>
           <t>2543..3259</t>
         </is>
       </c>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="H116" s="3" t="inlineStr">
         <is>
           <t>FR821780</t>
         </is>
       </c>
-      <c r="I116" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="J116" s="2" t="inlineStr">
+      <c r="I116" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="J116" s="3" t="inlineStr">
         <is>
           <t>NODE_37_length_4617_cov_2.071269:2543..3259:rep21_20_p020(pLGA251)_FR821780:94.700139</t>
         </is>
       </c>
-      <c r="K116" s="2" t="inlineStr">
+      <c r="K116" s="3" t="inlineStr">
         <is>
           <t>1..717</t>
         </is>
@@ -8827,48 +8827,48 @@
           <t>Q0003_MC00111</t>
         </is>
       </c>
-      <c r="B118" s="3" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
         <is>
           <t>Rep1</t>
         </is>
       </c>
-      <c r="C118" s="3" t="inlineStr">
+      <c r="C118" s="2" t="inlineStr">
         <is>
           <t>rep21</t>
         </is>
       </c>
-      <c r="D118" s="3" t="n">
+      <c r="D118" s="2" t="n">
         <v>94.7</v>
       </c>
-      <c r="E118" s="3" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>717/717</t>
         </is>
       </c>
-      <c r="F118" s="3" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>NODE_19_length_2420_cov_20.420410</t>
         </is>
       </c>
-      <c r="G118" s="3" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr">
         <is>
           <t>1364..2080</t>
         </is>
       </c>
-      <c r="H118" s="3" t="inlineStr">
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t>FR821780</t>
         </is>
       </c>
-      <c r="I118" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="J118" s="3" t="inlineStr">
+      <c r="I118" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="J118" s="2" t="inlineStr">
         <is>
           <t>NODE_19_length_2420_cov_20.420410:1364..2080:rep21_20_p020(pLGA251)_FR821780:94.700139</t>
         </is>
       </c>
-      <c r="K118" s="3" t="inlineStr">
+      <c r="K118" s="2" t="inlineStr">
         <is>
           <t>1..717</t>
         </is>
@@ -8880,48 +8880,48 @@
           <t>Q0003_MC00111</t>
         </is>
       </c>
-      <c r="B119" s="3" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
         <is>
           <t>Rep1</t>
         </is>
       </c>
-      <c r="C119" s="3" t="inlineStr">
+      <c r="C119" s="2" t="inlineStr">
         <is>
           <t>rep21</t>
         </is>
       </c>
-      <c r="D119" s="3" t="n">
+      <c r="D119" s="2" t="n">
         <v>90.31</v>
       </c>
-      <c r="E119" s="3" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>960/1005</t>
         </is>
       </c>
-      <c r="F119" s="3" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>NODE_26_length_962_cov_1.135329</t>
         </is>
       </c>
-      <c r="G119" s="3" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr">
         <is>
           <t>1..960</t>
         </is>
       </c>
-      <c r="H119" s="3" t="inlineStr">
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t>AM184102</t>
         </is>
       </c>
-      <c r="I119" s="3" t="n">
+      <c r="I119" s="2" t="n">
         <v>95.52</v>
       </c>
-      <c r="J119" s="3" t="inlineStr">
+      <c r="J119" s="2" t="inlineStr">
         <is>
           <t>NODE_26_length_962_cov_1.135329:1..960:rep21_27_rep(pLNU4)_AM184102:86.268657</t>
         </is>
       </c>
-      <c r="K119" s="3" t="inlineStr">
+      <c r="K119" s="2" t="inlineStr">
         <is>
           <t>21..980</t>
         </is>
@@ -9145,48 +9145,48 @@
           <t>R0051_BC00306</t>
         </is>
       </c>
-      <c r="B124" s="3" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
         <is>
           <t>Rep1</t>
         </is>
       </c>
-      <c r="C124" s="3" t="inlineStr">
+      <c r="C124" s="2" t="inlineStr">
         <is>
           <t>rep21</t>
         </is>
       </c>
-      <c r="D124" s="3" t="n">
+      <c r="D124" s="2" t="n">
         <v>90.05</v>
       </c>
-      <c r="E124" s="3" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>653/1005</t>
         </is>
       </c>
-      <c r="F124" s="3" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>NODE_62_length_3640_cov_10.337319</t>
         </is>
       </c>
-      <c r="G124" s="3" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr">
         <is>
           <t>1..653</t>
         </is>
       </c>
-      <c r="H124" s="3" t="inlineStr">
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>AM184102</t>
         </is>
       </c>
-      <c r="I124" s="3" t="n">
+      <c r="I124" s="2" t="n">
         <v>64.98</v>
       </c>
-      <c r="J124" s="3" t="inlineStr">
+      <c r="J124" s="2" t="inlineStr">
         <is>
           <t>NODE_62_length_3640_cov_10.337319:1..653:rep21_27_rep(pLNU4)_AM184102:58.507463</t>
         </is>
       </c>
-      <c r="K124" s="3" t="inlineStr">
+      <c r="K124" s="2" t="inlineStr">
         <is>
           <t>1..653</t>
         </is>
@@ -9516,48 +9516,48 @@
           <t>Q0003_BC00106</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
+      <c r="B131" s="3" t="inlineStr">
         <is>
           <t>Rep1</t>
         </is>
       </c>
-      <c r="C131" s="2" t="inlineStr">
+      <c r="C131" s="3" t="inlineStr">
         <is>
           <t>rep21</t>
         </is>
       </c>
-      <c r="D131" s="2" t="n">
+      <c r="D131" s="3" t="n">
         <v>94.56</v>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="E131" s="3" t="inlineStr">
         <is>
           <t>717/717</t>
         </is>
       </c>
-      <c r="F131" s="2" t="inlineStr">
+      <c r="F131" s="3" t="inlineStr">
         <is>
           <t>NODE_28_length_2765_cov_10.953753</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr">
+      <c r="G131" s="3" t="inlineStr">
         <is>
           <t>1749..2465</t>
         </is>
       </c>
-      <c r="H131" s="2" t="inlineStr">
+      <c r="H131" s="3" t="inlineStr">
         <is>
           <t>FR821780</t>
         </is>
       </c>
-      <c r="I131" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="J131" s="2" t="inlineStr">
+      <c r="I131" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="J131" s="3" t="inlineStr">
         <is>
           <t>NODE_28_length_2765_cov_10.953753:1749..2465:rep21_20_p020(pLGA251)_FR821780:94.560669</t>
         </is>
       </c>
-      <c r="K131" s="2" t="inlineStr">
+      <c r="K131" s="3" t="inlineStr">
         <is>
           <t>1..717</t>
         </is>
@@ -9675,48 +9675,48 @@
           <t>Q0003_BC00106</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
+      <c r="B134" s="3" t="inlineStr">
         <is>
           <t>Rep_trans</t>
         </is>
       </c>
-      <c r="C134" s="2" t="inlineStr">
+      <c r="C134" s="3" t="inlineStr">
         <is>
           <t>rep7c</t>
         </is>
       </c>
-      <c r="D134" s="2" t="n">
+      <c r="D134" s="3" t="n">
         <v>98.54000000000001</v>
       </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="E134" s="3" t="inlineStr">
         <is>
           <t>821/821</t>
         </is>
       </c>
-      <c r="F134" s="2" t="inlineStr">
+      <c r="F134" s="3" t="inlineStr">
         <is>
           <t>NODE_4_length_268507_cov_25.484034</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr">
+      <c r="G134" s="3" t="inlineStr">
         <is>
           <t>132578..133397</t>
         </is>
       </c>
-      <c r="H134" s="2" t="inlineStr">
+      <c r="H134" s="3" t="inlineStr">
         <is>
           <t>BX571857</t>
         </is>
       </c>
-      <c r="I134" s="2" t="n">
+      <c r="I134" s="3" t="n">
         <v>99.88</v>
       </c>
-      <c r="J134" s="2" t="inlineStr">
+      <c r="J134" s="3" t="inlineStr">
         <is>
           <t>NODE_4_length_268507_cov_25.484034:132578..133397:rep7c_1_rep(MSSA476)_BX571857:98.418345</t>
         </is>
       </c>
-      <c r="K134" s="2" t="inlineStr">
+      <c r="K134" s="3" t="inlineStr">
         <is>
           <t>1..821</t>
         </is>
@@ -9728,48 +9728,48 @@
           <t>Q0003_MC00214</t>
         </is>
       </c>
-      <c r="B135" s="3" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
         <is>
           <t>Rep1</t>
         </is>
       </c>
-      <c r="C135" s="3" t="inlineStr">
+      <c r="C135" s="2" t="inlineStr">
         <is>
           <t>rep21</t>
         </is>
       </c>
-      <c r="D135" s="3" t="n">
+      <c r="D135" s="2" t="n">
         <v>90.38</v>
       </c>
-      <c r="E135" s="3" t="inlineStr">
+      <c r="E135" s="2" t="inlineStr">
         <is>
           <t>988/1005</t>
         </is>
       </c>
-      <c r="F135" s="3" t="inlineStr">
+      <c r="F135" s="2" t="inlineStr">
         <is>
           <t>NODE_25_length_3640_cov_147.247652</t>
         </is>
       </c>
-      <c r="G135" s="3" t="inlineStr">
+      <c r="G135" s="2" t="inlineStr">
         <is>
           <t>1079..2066</t>
         </is>
       </c>
-      <c r="H135" s="3" t="inlineStr">
+      <c r="H135" s="2" t="inlineStr">
         <is>
           <t>AM184102</t>
         </is>
       </c>
-      <c r="I135" s="3" t="n">
+      <c r="I135" s="2" t="n">
         <v>98.31</v>
       </c>
-      <c r="J135" s="3" t="inlineStr">
+      <c r="J135" s="2" t="inlineStr">
         <is>
           <t>NODE_25_length_3640_cov_147.247652:1079..2066:rep21_27_rep(pLNU4)_AM184102:88.855721</t>
         </is>
       </c>
-      <c r="K135" s="3" t="inlineStr">
+      <c r="K135" s="2" t="inlineStr">
         <is>
           <t>1..988</t>
         </is>
@@ -9834,48 +9834,48 @@
           <t>Q0003_MC00214</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
+      <c r="B137" s="3" t="inlineStr">
         <is>
           <t>Rep_trans</t>
         </is>
       </c>
-      <c r="C137" s="2" t="inlineStr">
+      <c r="C137" s="3" t="inlineStr">
         <is>
           <t>rep7a</t>
         </is>
       </c>
-      <c r="D137" s="2" t="n">
+      <c r="D137" s="3" t="n">
         <v>99.89</v>
       </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="E137" s="3" t="inlineStr">
         <is>
           <t>945/945</t>
         </is>
       </c>
-      <c r="F137" s="2" t="inlineStr">
+      <c r="F137" s="3" t="inlineStr">
         <is>
           <t>NODE_23_length_4524_cov_31.321128</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr">
+      <c r="G137" s="3" t="inlineStr">
         <is>
           <t>2278..3222</t>
         </is>
       </c>
-      <c r="H137" s="2" t="inlineStr">
+      <c r="H137" s="3" t="inlineStr">
         <is>
           <t>NC005564</t>
         </is>
       </c>
-      <c r="I137" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="J137" s="2" t="inlineStr">
+      <c r="I137" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="J137" s="3" t="inlineStr">
         <is>
           <t>NODE_23_length_4524_cov_31.321128:2278..3222:rep7a_17_CDS4(pS194)_NC005564:99.894180</t>
         </is>
       </c>
-      <c r="K137" s="2" t="inlineStr">
+      <c r="K137" s="3" t="inlineStr">
         <is>
           <t>1..945</t>
         </is>
@@ -9887,48 +9887,48 @@
           <t>R0047_TC0201</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
+      <c r="B138" s="3" t="inlineStr">
         <is>
           <t>Rep1</t>
         </is>
       </c>
-      <c r="C138" s="2" t="inlineStr">
+      <c r="C138" s="3" t="inlineStr">
         <is>
           <t>rep21</t>
         </is>
       </c>
-      <c r="D138" s="2" t="n">
+      <c r="D138" s="3" t="n">
         <v>94.28</v>
       </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="E138" s="3" t="inlineStr">
         <is>
           <t>717/717</t>
         </is>
       </c>
-      <c r="F138" s="2" t="inlineStr">
+      <c r="F138" s="3" t="inlineStr">
         <is>
           <t>NODE_68_length_2635_cov_3.496379</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr">
+      <c r="G138" s="3" t="inlineStr">
         <is>
           <t>298..1014</t>
         </is>
       </c>
-      <c r="H138" s="2" t="inlineStr">
+      <c r="H138" s="3" t="inlineStr">
         <is>
           <t>FR821780</t>
         </is>
       </c>
-      <c r="I138" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="J138" s="2" t="inlineStr">
+      <c r="I138" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="J138" s="3" t="inlineStr">
         <is>
           <t>NODE_68_length_2635_cov_3.496379:298..1014:rep21_20_p020(pLGA251)_FR821780:94.281729</t>
         </is>
       </c>
-      <c r="K138" s="2" t="inlineStr">
+      <c r="K138" s="3" t="inlineStr">
         <is>
           <t>1..717</t>
         </is>
@@ -9940,48 +9940,48 @@
           <t>R0047_TC0201</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
+      <c r="B139" s="3" t="inlineStr">
         <is>
           <t>Rep_trans</t>
         </is>
       </c>
-      <c r="C139" s="2" t="inlineStr">
+      <c r="C139" s="3" t="inlineStr">
         <is>
           <t>rep7c</t>
         </is>
       </c>
-      <c r="D139" s="2" t="n">
+      <c r="D139" s="3" t="n">
         <v>98.54000000000001</v>
       </c>
-      <c r="E139" s="2" t="inlineStr">
+      <c r="E139" s="3" t="inlineStr">
         <is>
           <t>821/821</t>
         </is>
       </c>
-      <c r="F139" s="2" t="inlineStr">
+      <c r="F139" s="3" t="inlineStr">
         <is>
           <t>NODE_4_length_137025_cov_7.621923</t>
         </is>
       </c>
-      <c r="G139" s="2" t="inlineStr">
+      <c r="G139" s="3" t="inlineStr">
         <is>
           <t>127079..127898</t>
         </is>
       </c>
-      <c r="H139" s="2" t="inlineStr">
+      <c r="H139" s="3" t="inlineStr">
         <is>
           <t>BX571857</t>
         </is>
       </c>
-      <c r="I139" s="2" t="n">
+      <c r="I139" s="3" t="n">
         <v>99.88</v>
       </c>
-      <c r="J139" s="2" t="inlineStr">
+      <c r="J139" s="3" t="inlineStr">
         <is>
           <t>NODE_4_length_137025_cov_7.621923:127079..127898:rep7c_1_rep(MSSA476)_BX571857:98.418345</t>
         </is>
       </c>
-      <c r="K139" s="2" t="inlineStr">
+      <c r="K139" s="3" t="inlineStr">
         <is>
           <t>1..821</t>
         </is>
@@ -10046,48 +10046,48 @@
           <t>Q0003_MC00215</t>
         </is>
       </c>
-      <c r="B141" s="3" t="inlineStr">
+      <c r="B141" s="2" t="inlineStr">
         <is>
           <t>Rep1</t>
         </is>
       </c>
-      <c r="C141" s="3" t="inlineStr">
+      <c r="C141" s="2" t="inlineStr">
         <is>
           <t>rep21</t>
         </is>
       </c>
-      <c r="D141" s="3" t="n">
+      <c r="D141" s="2" t="n">
         <v>90.12</v>
       </c>
-      <c r="E141" s="3" t="inlineStr">
+      <c r="E141" s="2" t="inlineStr">
         <is>
           <t>658/1005</t>
         </is>
       </c>
-      <c r="F141" s="3" t="inlineStr">
+      <c r="F141" s="2" t="inlineStr">
         <is>
           <t>NODE_21_length_3640_cov_7071.160262</t>
         </is>
       </c>
-      <c r="G141" s="3" t="inlineStr">
+      <c r="G141" s="2" t="inlineStr">
         <is>
           <t>2983..3640</t>
         </is>
       </c>
-      <c r="H141" s="3" t="inlineStr">
+      <c r="H141" s="2" t="inlineStr">
         <is>
           <t>AM184102</t>
         </is>
       </c>
-      <c r="I141" s="3" t="n">
+      <c r="I141" s="2" t="n">
         <v>65.47</v>
       </c>
-      <c r="J141" s="3" t="inlineStr">
+      <c r="J141" s="2" t="inlineStr">
         <is>
           <t>NODE_21_length_3640_cov_7071.160262:2983..3640:rep21_27_rep(pLNU4)_AM184102:59.004975</t>
         </is>
       </c>
-      <c r="K141" s="3" t="inlineStr">
+      <c r="K141" s="2" t="inlineStr">
         <is>
           <t>1..658</t>
         </is>
@@ -10152,48 +10152,48 @@
           <t>Q0003_MC00215</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
+      <c r="B143" s="3" t="inlineStr">
         <is>
           <t>Rep_trans</t>
         </is>
       </c>
-      <c r="C143" s="2" t="inlineStr">
+      <c r="C143" s="3" t="inlineStr">
         <is>
           <t>rep7a</t>
         </is>
       </c>
-      <c r="D143" s="2" t="n">
+      <c r="D143" s="3" t="n">
         <v>99.89</v>
       </c>
-      <c r="E143" s="2" t="inlineStr">
+      <c r="E143" s="3" t="inlineStr">
         <is>
           <t>945/945</t>
         </is>
       </c>
-      <c r="F143" s="2" t="inlineStr">
+      <c r="F143" s="3" t="inlineStr">
         <is>
           <t>NODE_19_length_4524_cov_2975.045486</t>
         </is>
       </c>
-      <c r="G143" s="2" t="inlineStr">
+      <c r="G143" s="3" t="inlineStr">
         <is>
           <t>2680..3624</t>
         </is>
       </c>
-      <c r="H143" s="2" t="inlineStr">
+      <c r="H143" s="3" t="inlineStr">
         <is>
           <t>NC005564</t>
         </is>
       </c>
-      <c r="I143" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="J143" s="2" t="inlineStr">
+      <c r="I143" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="J143" s="3" t="inlineStr">
         <is>
           <t>NODE_19_length_4524_cov_2975.045486:2680..3624:rep7a_17_CDS4(pS194)_NC005564:99.894180</t>
         </is>
       </c>
-      <c r="K143" s="2" t="inlineStr">
+      <c r="K143" s="3" t="inlineStr">
         <is>
           <t>1..945</t>
         </is>
@@ -10232,7 +10232,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="2" t="n"/>
+      <c r="B4" s="3" t="n"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>The light green colour indicates a warning due to a non-perfect match: %ID  &lt;  100%, HSP length = plasmid length</t>
@@ -10248,7 +10248,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="3" t="n"/>
+      <c r="B6" s="2" t="n"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>The red colour indicates either that no gene was found (None), or that the given match was under the threshold: HSP  &lt;  plasmid length, %ID  &lt;  95%.</t>
